--- a/research/traditional_assets/database/data/morocco/morocco_transportation.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_transportation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1087039974486549</v>
+        <v>0.1083867446568192</v>
       </c>
       <c r="C2">
-        <v>162.5080035459373</v>
+        <v>161.5998554925135</v>
       </c>
       <c r="D2">
-        <v>157.3980035459373</v>
+        <v>158.1958554925135</v>
       </c>
       <c r="E2">
-        <v>-37.9</v>
+        <v>-36.194</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.706</v>
       </c>
       <c r="G2">
         <v>5.11</v>
@@ -1451,28 +1451,28 @@
         <v>3.66</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08581179999999999</v>
       </c>
       <c r="N2">
-        <v>3.66</v>
+        <v>3.5741882</v>
       </c>
       <c r="O2">
-        <v>1.1712</v>
+        <v>1.143740224</v>
       </c>
       <c r="P2">
-        <v>2.4888</v>
+        <v>2.430447976</v>
       </c>
       <c r="Q2">
-        <v>11.7288</v>
+        <v>11.670447976</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1087039974486549</v>
+        <v>0.1091360653099184</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8254812525725722</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>42.65147683651899</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1083867446568192</v>
+        <v>0.1080694918649835</v>
       </c>
       <c r="C3">
-        <v>161.5998554925135</v>
+        <v>160.6998372872688</v>
       </c>
       <c r="D3">
-        <v>158.1958554925135</v>
+        <v>159.0018372872688</v>
       </c>
       <c r="E3">
-        <v>-36.194</v>
+        <v>-34.488</v>
       </c>
       <c r="F3">
-        <v>1.706</v>
+        <v>3.412</v>
       </c>
       <c r="G3">
         <v>5.11</v>
@@ -1533,28 +1533,28 @@
         <v>3.66</v>
       </c>
       <c r="M3">
-        <v>0.08581179999999999</v>
+        <v>0.1716236</v>
       </c>
       <c r="N3">
-        <v>3.5741882</v>
+        <v>3.4883764</v>
       </c>
       <c r="O3">
-        <v>1.143740224</v>
+        <v>1.116280448</v>
       </c>
       <c r="P3">
-        <v>2.430447976</v>
+        <v>2.372095952</v>
       </c>
       <c r="Q3">
-        <v>11.670447976</v>
+        <v>11.612095952</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1091360653099184</v>
+        <v>0.1095769508826363</v>
       </c>
       <c r="T3">
-        <v>0.8254812525725722</v>
+        <v>0.8312274695664356</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>42.65147683651899</v>
+        <v>21.32573841825949</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1080694918649835</v>
+        <v>0.1077522390731478</v>
       </c>
       <c r="C4">
-        <v>160.6998372872688</v>
+        <v>159.80807382724</v>
       </c>
       <c r="D4">
-        <v>159.0018372872688</v>
+        <v>159.81607382724</v>
       </c>
       <c r="E4">
-        <v>-34.488</v>
+        <v>-32.782</v>
       </c>
       <c r="F4">
-        <v>3.412</v>
+        <v>5.117999999999999</v>
       </c>
       <c r="G4">
         <v>5.11</v>
@@ -1615,28 +1615,28 @@
         <v>3.66</v>
       </c>
       <c r="M4">
-        <v>0.1716236</v>
+        <v>0.2574354</v>
       </c>
       <c r="N4">
-        <v>3.4883764</v>
+        <v>3.4025646</v>
       </c>
       <c r="O4">
-        <v>1.116280448</v>
+        <v>1.088820672</v>
       </c>
       <c r="P4">
-        <v>2.372095952</v>
+        <v>2.313743928</v>
       </c>
       <c r="Q4">
-        <v>11.612095952</v>
+        <v>11.553743928</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1095769508826363</v>
+        <v>0.1100269268795339</v>
       </c>
       <c r="T4">
-        <v>0.8312274695664356</v>
+        <v>0.8370921652612036</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>21.32573841825949</v>
+        <v>14.21715894550633</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1077522390731478</v>
+        <v>0.1074757862813121</v>
       </c>
       <c r="C5">
-        <v>159.80807382724</v>
+        <v>158.8184262639685</v>
       </c>
       <c r="D5">
-        <v>159.81607382724</v>
+        <v>160.5324262639685</v>
       </c>
       <c r="E5">
-        <v>-32.782</v>
+        <v>-31.076</v>
       </c>
       <c r="F5">
-        <v>5.117999999999999</v>
+        <v>6.824</v>
       </c>
       <c r="G5">
         <v>5.11</v>
@@ -1697,45 +1697,45 @@
         <v>3.66</v>
       </c>
       <c r="M5">
-        <v>0.2574354</v>
+        <v>0.3534832</v>
       </c>
       <c r="N5">
-        <v>3.4025646</v>
+        <v>3.3065168</v>
       </c>
       <c r="O5">
-        <v>1.088820672</v>
+        <v>1.058085376</v>
       </c>
       <c r="P5">
-        <v>2.313743928</v>
+        <v>2.248431424</v>
       </c>
       <c r="Q5">
-        <v>11.553743928</v>
+        <v>11.488431424</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1100269268795339</v>
+        <v>0.1104862773763668</v>
       </c>
       <c r="T5">
-        <v>0.8370921652612036</v>
+        <v>0.8430790421162792</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.32</v>
       </c>
       <c r="W5">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>14.21715894550633</v>
+        <v>10.35409886523603</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1074757862813121</v>
+        <v>0.1072265334894765</v>
       </c>
       <c r="C6">
-        <v>158.8184262639685</v>
+        <v>157.7638248234087</v>
       </c>
       <c r="D6">
-        <v>160.5324262639685</v>
+        <v>161.1838248234087</v>
       </c>
       <c r="E6">
-        <v>-31.076</v>
+        <v>-29.37</v>
       </c>
       <c r="F6">
-        <v>6.824</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G6">
         <v>5.11</v>
@@ -1779,45 +1779,45 @@
         <v>3.66</v>
       </c>
       <c r="M6">
-        <v>0.3534832</v>
+        <v>0.456355</v>
       </c>
       <c r="N6">
-        <v>3.3065168</v>
+        <v>3.203645</v>
       </c>
       <c r="O6">
-        <v>1.058085376</v>
+        <v>1.0251664</v>
       </c>
       <c r="P6">
-        <v>2.248431424</v>
+        <v>2.1784786</v>
       </c>
       <c r="Q6">
-        <v>11.488431424</v>
+        <v>11.4184786</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1104862773763668</v>
+        <v>0.1109552984099752</v>
       </c>
       <c r="T6">
-        <v>0.8430790421162792</v>
+        <v>0.8491919584840932</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.32</v>
       </c>
       <c r="W6">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>10.35409886523603</v>
+        <v>8.020072092997777</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1072265334894765</v>
+        <v>0.1069636806976408</v>
       </c>
       <c r="C7">
-        <v>157.7638248234087</v>
+        <v>156.7505172492133</v>
       </c>
       <c r="D7">
-        <v>161.1838248234087</v>
+        <v>161.8765172492133</v>
       </c>
       <c r="E7">
-        <v>-29.37</v>
+        <v>-27.664</v>
       </c>
       <c r="F7">
-        <v>8.529999999999999</v>
+        <v>10.236</v>
       </c>
       <c r="G7">
         <v>5.11</v>
@@ -1861,45 +1861,45 @@
         <v>3.66</v>
       </c>
       <c r="M7">
-        <v>0.456355</v>
+        <v>0.5558148000000001</v>
       </c>
       <c r="N7">
-        <v>3.203645</v>
+        <v>3.1041852</v>
       </c>
       <c r="O7">
-        <v>1.0251664</v>
+        <v>0.9933392639999999</v>
       </c>
       <c r="P7">
-        <v>2.1784786</v>
+        <v>2.110845936</v>
       </c>
       <c r="Q7">
-        <v>11.4184786</v>
+        <v>11.350845936</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1109552984099752</v>
+        <v>0.1114342986145115</v>
       </c>
       <c r="T7">
-        <v>0.8491919584840932</v>
+        <v>0.8554349369022862</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.32</v>
       </c>
       <c r="W7">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.020072092997777</v>
+        <v>6.584927209566927</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1069636806976408</v>
+        <v>0.1067212279058051</v>
       </c>
       <c r="C8">
-        <v>156.7505172492133</v>
+        <v>155.688749397659</v>
       </c>
       <c r="D8">
-        <v>161.8765172492133</v>
+        <v>162.520749397659</v>
       </c>
       <c r="E8">
-        <v>-27.664</v>
+        <v>-25.958</v>
       </c>
       <c r="F8">
-        <v>10.236</v>
+        <v>11.942</v>
       </c>
       <c r="G8">
         <v>5.11</v>
@@ -1943,45 +1943,45 @@
         <v>3.66</v>
       </c>
       <c r="M8">
-        <v>0.5558147999999999</v>
+        <v>0.6603925999999999</v>
       </c>
       <c r="N8">
-        <v>3.1041852</v>
+        <v>2.9996074</v>
       </c>
       <c r="O8">
-        <v>0.9933392640000002</v>
+        <v>0.9598743680000001</v>
       </c>
       <c r="P8">
-        <v>2.110845936</v>
+        <v>2.039733032</v>
       </c>
       <c r="Q8">
-        <v>11.350845936</v>
+        <v>11.279733032</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1114342986145115</v>
+        <v>0.1119235998987151</v>
       </c>
       <c r="T8">
-        <v>0.8554349369022862</v>
+        <v>0.8618121729208705</v>
       </c>
       <c r="U8">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V8">
         <v>0.32</v>
       </c>
       <c r="W8">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.584927209566929</v>
+        <v>5.542157801283662</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1067212279058051</v>
+        <v>0.1064379751139694</v>
       </c>
       <c r="C9">
-        <v>155.6887493976591</v>
+        <v>154.7419181514243</v>
       </c>
       <c r="D9">
-        <v>162.520749397659</v>
+        <v>163.2799181514243</v>
       </c>
       <c r="E9">
-        <v>-25.958</v>
+        <v>-24.252</v>
       </c>
       <c r="F9">
-        <v>11.942</v>
+        <v>13.648</v>
       </c>
       <c r="G9">
         <v>5.11</v>
@@ -2025,28 +2025,28 @@
         <v>3.66</v>
       </c>
       <c r="M9">
-        <v>0.6603926</v>
+        <v>0.7547344</v>
       </c>
       <c r="N9">
-        <v>2.9996074</v>
+        <v>2.9052656</v>
       </c>
       <c r="O9">
-        <v>0.9598743680000001</v>
+        <v>0.929684992</v>
       </c>
       <c r="P9">
-        <v>2.039733032</v>
+        <v>1.975580608</v>
       </c>
       <c r="Q9">
-        <v>11.279733032</v>
+        <v>11.215580608</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1119235998987151</v>
+        <v>0.112423538167358</v>
       </c>
       <c r="T9">
-        <v>0.8618121729208705</v>
+        <v>0.8683280445050762</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.542157801283661</v>
+        <v>4.849388076123203</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1064379751139694</v>
+        <v>0.1063077223221337</v>
       </c>
       <c r="C10">
-        <v>154.7419181514243</v>
+        <v>153.3874049430886</v>
       </c>
       <c r="D10">
-        <v>163.2799181514243</v>
+        <v>163.6314049430886</v>
       </c>
       <c r="E10">
-        <v>-24.252</v>
+        <v>-22.546</v>
       </c>
       <c r="F10">
-        <v>13.648</v>
+        <v>15.354</v>
       </c>
       <c r="G10">
         <v>5.11</v>
@@ -2107,45 +2107,45 @@
         <v>3.66</v>
       </c>
       <c r="M10">
-        <v>0.7547344</v>
+        <v>0.8874612000000001</v>
       </c>
       <c r="N10">
-        <v>2.9052656</v>
+        <v>2.7725388</v>
       </c>
       <c r="O10">
-        <v>0.929684992</v>
+        <v>0.887212416</v>
       </c>
       <c r="P10">
-        <v>1.975580608</v>
+        <v>1.885326384</v>
       </c>
       <c r="Q10">
-        <v>11.215580608</v>
+        <v>11.125326384</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.112423538167358</v>
+        <v>0.1129344640902568</v>
       </c>
       <c r="T10">
-        <v>0.8683280445050762</v>
+        <v>0.8749871220581655</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.849388076123203</v>
+        <v>4.124123961701086</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1063077223221337</v>
+        <v>0.106469869530298</v>
       </c>
       <c r="C11">
-        <v>153.3874049430886</v>
+        <v>151.2440811827948</v>
       </c>
       <c r="D11">
-        <v>163.6314049430886</v>
+        <v>163.1940811827948</v>
       </c>
       <c r="E11">
-        <v>-22.546</v>
+        <v>-20.84</v>
       </c>
       <c r="F11">
-        <v>15.354</v>
+        <v>17.06</v>
       </c>
       <c r="G11">
         <v>5.11</v>
@@ -2189,45 +2189,45 @@
         <v>3.66</v>
       </c>
       <c r="M11">
-        <v>0.8874612000000001</v>
+        <v>1.093546</v>
       </c>
       <c r="N11">
-        <v>2.7725388</v>
+        <v>2.566454</v>
       </c>
       <c r="O11">
-        <v>0.887212416</v>
+        <v>0.8212652800000001</v>
       </c>
       <c r="P11">
-        <v>1.885326384</v>
+        <v>1.74518872</v>
       </c>
       <c r="Q11">
-        <v>11.125326384</v>
+        <v>10.98518872</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1129344640902568</v>
+        <v>0.1134567439225533</v>
       </c>
       <c r="T11">
-        <v>0.8749871220581655</v>
+        <v>0.8817941791124346</v>
       </c>
       <c r="U11">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.039304</v>
+        <v>0.043588</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.124123961701086</v>
+        <v>3.346909960806404</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.106469869530298</v>
+        <v>0.1062464567384623</v>
       </c>
       <c r="C12">
-        <v>151.2440811827948</v>
+        <v>150.1412537632136</v>
       </c>
       <c r="D12">
-        <v>163.1940811827948</v>
+        <v>163.7972537632136</v>
       </c>
       <c r="E12">
-        <v>-20.84</v>
+        <v>-19.134</v>
       </c>
       <c r="F12">
-        <v>17.06</v>
+        <v>18.766</v>
       </c>
       <c r="G12">
         <v>5.11</v>
@@ -2271,28 +2271,28 @@
         <v>3.66</v>
       </c>
       <c r="M12">
-        <v>1.093546</v>
+        <v>1.2029006</v>
       </c>
       <c r="N12">
-        <v>2.566454</v>
+        <v>2.4570994</v>
       </c>
       <c r="O12">
-        <v>0.8212652800000001</v>
+        <v>0.7862718080000001</v>
       </c>
       <c r="P12">
-        <v>1.74518872</v>
+        <v>1.670827592</v>
       </c>
       <c r="Q12">
-        <v>10.98518872</v>
+        <v>10.910827592</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1134567439225533</v>
+        <v>0.1139907603802947</v>
       </c>
       <c r="T12">
-        <v>0.8817941791124346</v>
+        <v>0.8887542037409569</v>
       </c>
       <c r="U12">
         <v>0.0641</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.346909960806404</v>
+        <v>3.042645418914913</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1062464567384623</v>
+        <v>0.1069777639466266</v>
       </c>
       <c r="C13">
-        <v>150.1412537632136</v>
+        <v>146.477252936981</v>
       </c>
       <c r="D13">
-        <v>163.7972537632136</v>
+        <v>161.839252936981</v>
       </c>
       <c r="E13">
-        <v>-19.134</v>
+        <v>-17.428</v>
       </c>
       <c r="F13">
-        <v>18.766</v>
+        <v>20.472</v>
       </c>
       <c r="G13">
         <v>5.11</v>
@@ -2353,45 +2353,45 @@
         <v>3.66</v>
       </c>
       <c r="M13">
-        <v>1.2029006</v>
+        <v>1.5517776</v>
       </c>
       <c r="N13">
-        <v>2.4570994</v>
+        <v>2.1082224</v>
       </c>
       <c r="O13">
-        <v>0.7862718080000001</v>
+        <v>0.6746311680000001</v>
       </c>
       <c r="P13">
-        <v>1.670827592</v>
+        <v>1.433591232</v>
       </c>
       <c r="Q13">
-        <v>10.910827592</v>
+        <v>10.673591232</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1139907603802947</v>
+        <v>0.114536913575712</v>
       </c>
       <c r="T13">
-        <v>0.8887542037409569</v>
+        <v>0.8958724107474002</v>
       </c>
       <c r="U13">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.043588</v>
+        <v>0.051544</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.042645418914913</v>
+        <v>2.358585405537495</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1069777639466266</v>
+        <v>0.1068339111547909</v>
       </c>
       <c r="C14">
-        <v>146.477252936981</v>
+        <v>145.1526970870134</v>
       </c>
       <c r="D14">
-        <v>161.839252936981</v>
+        <v>162.2206970870134</v>
       </c>
       <c r="E14">
-        <v>-17.428</v>
+        <v>-15.722</v>
       </c>
       <c r="F14">
-        <v>20.472</v>
+        <v>22.178</v>
       </c>
       <c r="G14">
         <v>5.11</v>
@@ -2435,28 +2435,28 @@
         <v>3.66</v>
       </c>
       <c r="M14">
-        <v>1.5517776</v>
+        <v>1.6810924</v>
       </c>
       <c r="N14">
-        <v>2.1082224</v>
+        <v>1.9789076</v>
       </c>
       <c r="O14">
-        <v>0.6746311680000001</v>
+        <v>0.633250432</v>
       </c>
       <c r="P14">
-        <v>1.433591232</v>
+        <v>1.345657168</v>
       </c>
       <c r="Q14">
-        <v>10.673591232</v>
+        <v>10.585657168</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.114536913575712</v>
+        <v>0.115095622017001</v>
       </c>
       <c r="T14">
-        <v>0.8958724107474002</v>
+        <v>0.9031542546965203</v>
       </c>
       <c r="U14">
         <v>0.07580000000000001</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.358585405537495</v>
+        <v>2.177155758957687</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1068339111547909</v>
+        <v>0.1066900583629552</v>
       </c>
       <c r="C15">
-        <v>145.1526970870134</v>
+        <v>143.8299435610174</v>
       </c>
       <c r="D15">
-        <v>162.2206970870134</v>
+        <v>162.6039435610174</v>
       </c>
       <c r="E15">
-        <v>-15.722</v>
+        <v>-14.016</v>
       </c>
       <c r="F15">
-        <v>22.178</v>
+        <v>23.884</v>
       </c>
       <c r="G15">
         <v>5.11</v>
@@ -2517,28 +2517,28 @@
         <v>3.66</v>
       </c>
       <c r="M15">
-        <v>1.6810924</v>
+        <v>1.8104072</v>
       </c>
       <c r="N15">
-        <v>1.9789076</v>
+        <v>1.8495928</v>
       </c>
       <c r="O15">
-        <v>0.633250432</v>
+        <v>0.5918696959999999</v>
       </c>
       <c r="P15">
-        <v>1.345657168</v>
+        <v>1.257723104</v>
       </c>
       <c r="Q15">
-        <v>10.585657168</v>
+        <v>10.497723104</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.115095622017001</v>
+        <v>0.1156673236778549</v>
       </c>
       <c r="T15">
-        <v>0.9031542546965203</v>
+        <v>0.9106054438537595</v>
       </c>
       <c r="U15">
         <v>0.07580000000000001</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.177155758957687</v>
+        <v>2.021644633317853</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1066900583629552</v>
+        <v>0.1079946055711195</v>
       </c>
       <c r="C16">
-        <v>143.8299435610174</v>
+        <v>138.7132856967036</v>
       </c>
       <c r="D16">
-        <v>162.6039435610174</v>
+        <v>159.1932856967036</v>
       </c>
       <c r="E16">
-        <v>-14.016</v>
+        <v>-12.31</v>
       </c>
       <c r="F16">
-        <v>23.884</v>
+        <v>25.59</v>
       </c>
       <c r="G16">
         <v>5.11</v>
@@ -2599,45 +2599,45 @@
         <v>3.66</v>
       </c>
       <c r="M16">
-        <v>1.8104072</v>
+        <v>2.3031</v>
       </c>
       <c r="N16">
-        <v>1.8495928</v>
+        <v>1.3569</v>
       </c>
       <c r="O16">
-        <v>0.5918696959999999</v>
+        <v>0.434208</v>
       </c>
       <c r="P16">
-        <v>1.257723104</v>
+        <v>0.9226920000000001</v>
       </c>
       <c r="Q16">
-        <v>10.497723104</v>
+        <v>10.162692</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1156673236778549</v>
+        <v>0.1162524771424935</v>
       </c>
       <c r="T16">
-        <v>0.9106054438537595</v>
+        <v>0.9182319551088163</v>
       </c>
       <c r="U16">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.021644633317853</v>
+        <v>1.589162433242152</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1079946055711195</v>
+        <v>0.1150570761398321</v>
       </c>
       <c r="C17">
-        <v>138.7132856967036</v>
+        <v>120.7735958322971</v>
       </c>
       <c r="D17">
-        <v>159.1932856967036</v>
+        <v>142.9595958322971</v>
       </c>
       <c r="E17">
-        <v>-12.31</v>
+        <v>-10.604</v>
       </c>
       <c r="F17">
-        <v>25.59</v>
+        <v>27.296</v>
       </c>
       <c r="G17">
         <v>5.11</v>
@@ -2681,45 +2681,45 @@
         <v>3.66</v>
       </c>
       <c r="M17">
-        <v>2.3031</v>
+        <v>4.0070528</v>
       </c>
       <c r="N17">
-        <v>1.3569</v>
+        <v>-0.3470528000000002</v>
       </c>
       <c r="O17">
-        <v>0.4342080000000001</v>
+        <v>-0.1110568960000001</v>
       </c>
       <c r="P17">
-        <v>0.9226920000000003</v>
+        <v>-0.2359959040000001</v>
       </c>
       <c r="Q17">
-        <v>10.162692</v>
+        <v>9.004004096000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1162524771424935</v>
+        <v>0.1171836402993311</v>
       </c>
       <c r="T17">
-        <v>0.9182319551088163</v>
+        <v>0.9303681325820224</v>
       </c>
       <c r="U17">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V17">
-        <v>0.32</v>
+        <v>0.2922846437161996</v>
       </c>
       <c r="W17">
-        <v>0.06119999999999999</v>
+        <v>0.1038926143024619</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y17">
-        <v>1.589162433242152</v>
+        <v>0.9133895116131237</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1150570761398321</v>
+        <v>0.1160670761398321</v>
       </c>
       <c r="C18">
-        <v>120.7735958322971</v>
+        <v>117.0127331608621</v>
       </c>
       <c r="D18">
-        <v>142.9595958322971</v>
+        <v>140.9047331608621</v>
       </c>
       <c r="E18">
-        <v>-10.604</v>
+        <v>-8.897999999999996</v>
       </c>
       <c r="F18">
-        <v>27.296</v>
+        <v>29.002</v>
       </c>
       <c r="G18">
         <v>5.11</v>
@@ -2763,37 +2763,37 @@
         <v>3.66</v>
       </c>
       <c r="M18">
-        <v>4.0070528</v>
+        <v>4.257493600000001</v>
       </c>
       <c r="N18">
-        <v>-0.3470528000000002</v>
+        <v>-0.5974936000000008</v>
       </c>
       <c r="O18">
-        <v>-0.1110568960000001</v>
+        <v>-0.1911979520000003</v>
       </c>
       <c r="P18">
-        <v>-0.2359959040000001</v>
+        <v>-0.4062956480000006</v>
       </c>
       <c r="Q18">
-        <v>9.004004096000001</v>
+        <v>8.833704352</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1171836402993311</v>
+        <v>0.1180436841583592</v>
       </c>
       <c r="T18">
-        <v>0.9303681325820224</v>
+        <v>0.9415773871914443</v>
       </c>
       <c r="U18">
         <v>0.1468</v>
       </c>
       <c r="V18">
-        <v>0.2922846437161996</v>
+        <v>0.2750914293799525</v>
       </c>
       <c r="W18">
-        <v>0.1038926143024619</v>
+        <v>0.106416578167023</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.9133895116131237</v>
+        <v>0.8596607168123516</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1160670761398321</v>
+        <v>0.1170770761398321</v>
       </c>
       <c r="C19">
-        <v>117.0127331608621</v>
+        <v>113.3101055184308</v>
       </c>
       <c r="D19">
-        <v>140.9047331608621</v>
+        <v>138.9081055184308</v>
       </c>
       <c r="E19">
-        <v>-8.897999999999996</v>
+        <v>-7.191999999999997</v>
       </c>
       <c r="F19">
-        <v>29.002</v>
+        <v>30.708</v>
       </c>
       <c r="G19">
         <v>5.11</v>
@@ -2845,37 +2845,37 @@
         <v>3.66</v>
       </c>
       <c r="M19">
-        <v>4.257493600000001</v>
+        <v>4.507934400000001</v>
       </c>
       <c r="N19">
-        <v>-0.5974936000000008</v>
+        <v>-0.8479344000000006</v>
       </c>
       <c r="O19">
-        <v>-0.1911979520000003</v>
+        <v>-0.2713390080000002</v>
       </c>
       <c r="P19">
-        <v>-0.4062956480000006</v>
+        <v>-0.5765953920000004</v>
       </c>
       <c r="Q19">
-        <v>8.833704352</v>
+        <v>8.663404608</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1180436841583592</v>
+        <v>0.1189247046968758</v>
       </c>
       <c r="T19">
-        <v>0.9415773871914443</v>
+        <v>0.9530600382547545</v>
       </c>
       <c r="U19">
         <v>0.1468</v>
       </c>
       <c r="V19">
-        <v>0.2750914293799525</v>
+        <v>0.2598085721921774</v>
       </c>
       <c r="W19">
-        <v>0.106416578167023</v>
+        <v>0.1086601016021884</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.8596607168123516</v>
+        <v>0.8119017881005544</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1170770761398321</v>
+        <v>0.1291381814099999</v>
       </c>
       <c r="C20">
-        <v>113.3101055184308</v>
+        <v>91.50065167300829</v>
       </c>
       <c r="D20">
-        <v>138.9081055184308</v>
+        <v>118.8046516730083</v>
       </c>
       <c r="E20">
-        <v>-7.192</v>
+        <v>-5.485999999999997</v>
       </c>
       <c r="F20">
-        <v>30.708</v>
+        <v>32.414</v>
       </c>
       <c r="G20">
         <v>5.11</v>
@@ -2927,45 +2927,45 @@
         <v>3.66</v>
       </c>
       <c r="M20">
-        <v>4.5079344</v>
+        <v>6.508731200000001</v>
       </c>
       <c r="N20">
-        <v>-0.8479343999999998</v>
+        <v>-2.8487312</v>
       </c>
       <c r="O20">
-        <v>-0.2713390079999999</v>
+        <v>-0.9115939840000001</v>
       </c>
       <c r="P20">
-        <v>-0.5765953919999998</v>
+        <v>-1.937137216</v>
       </c>
       <c r="Q20">
-        <v>8.663404608</v>
+        <v>7.302862784</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1189247046968758</v>
+        <v>0.1208041520019827</v>
       </c>
       <c r="T20">
-        <v>0.9530600382547545</v>
+        <v>0.9775555371142466</v>
       </c>
       <c r="U20">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.2598085721921775</v>
+        <v>0.1799429050012082</v>
       </c>
       <c r="W20">
-        <v>0.1086601016021884</v>
+        <v>0.1646674646757574</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.8119017881005545</v>
+        <v>0.5623215781287756</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1291381814099999</v>
+        <v>0.1306881814099999</v>
       </c>
       <c r="C21">
-        <v>91.50065167300829</v>
+        <v>87.62536017642466</v>
       </c>
       <c r="D21">
-        <v>118.8046516730083</v>
+        <v>116.6353601764247</v>
       </c>
       <c r="E21">
-        <v>-5.485999999999997</v>
+        <v>-3.780000000000001</v>
       </c>
       <c r="F21">
-        <v>32.414</v>
+        <v>34.12</v>
       </c>
       <c r="G21">
         <v>5.11</v>
@@ -3009,37 +3009,37 @@
         <v>3.66</v>
       </c>
       <c r="M21">
-        <v>6.508731200000001</v>
+        <v>6.851296</v>
       </c>
       <c r="N21">
-        <v>-2.8487312</v>
+        <v>-3.191295999999999</v>
       </c>
       <c r="O21">
-        <v>-0.9115939840000001</v>
+        <v>-1.02121472</v>
       </c>
       <c r="P21">
-        <v>-1.937137216</v>
+        <v>-2.17008128</v>
       </c>
       <c r="Q21">
-        <v>7.302862784</v>
+        <v>7.06991872</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1208041520019827</v>
+        <v>0.1217417039020075</v>
       </c>
       <c r="T21">
-        <v>0.9775555371142466</v>
+        <v>0.9897749813281747</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.1799429050012082</v>
+        <v>0.1709457597511478</v>
       </c>
       <c r="W21">
-        <v>0.1646674646757574</v>
+        <v>0.1664740914419695</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.5623215781287756</v>
+        <v>0.534205499222337</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1306881814099999</v>
+        <v>0.13223818141</v>
       </c>
       <c r="C22">
-        <v>87.62536017642466</v>
+        <v>83.82786767479567</v>
       </c>
       <c r="D22">
-        <v>116.6353601764247</v>
+        <v>114.5438676747957</v>
       </c>
       <c r="E22">
-        <v>-3.780000000000001</v>
+        <v>-2.073999999999998</v>
       </c>
       <c r="F22">
-        <v>34.12</v>
+        <v>35.826</v>
       </c>
       <c r="G22">
         <v>5.11</v>
@@ -3091,37 +3091,37 @@
         <v>3.66</v>
       </c>
       <c r="M22">
-        <v>6.851296</v>
+        <v>7.1938608</v>
       </c>
       <c r="N22">
-        <v>-3.191295999999999</v>
+        <v>-3.5338608</v>
       </c>
       <c r="O22">
-        <v>-1.02121472</v>
+        <v>-1.130835456</v>
       </c>
       <c r="P22">
-        <v>-2.17008128</v>
+        <v>-2.403025344</v>
       </c>
       <c r="Q22">
-        <v>7.06991872</v>
+        <v>6.836974656</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1217417039020075</v>
+        <v>0.1227029912931722</v>
       </c>
       <c r="T22">
-        <v>0.9897749813281747</v>
+        <v>1.002303778560177</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.1709457597511478</v>
+        <v>0.1628054854772836</v>
       </c>
       <c r="W22">
-        <v>0.1664740914419695</v>
+        <v>0.1681086585161615</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.534205499222337</v>
+        <v>0.5087671421165114</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1322381814099999</v>
+        <v>0.1418074019420046</v>
       </c>
       <c r="C23">
-        <v>83.8278676747957</v>
+        <v>70.70508617464631</v>
       </c>
       <c r="D23">
-        <v>114.5438676747957</v>
+        <v>103.1270861746463</v>
       </c>
       <c r="E23">
-        <v>-2.073999999999998</v>
+        <v>-0.3680000000000021</v>
       </c>
       <c r="F23">
-        <v>35.826</v>
+        <v>37.532</v>
       </c>
       <c r="G23">
         <v>5.11</v>
@@ -3173,45 +3173,45 @@
         <v>3.66</v>
       </c>
       <c r="M23">
-        <v>7.1938608</v>
+        <v>8.8500456</v>
       </c>
       <c r="N23">
-        <v>-3.5338608</v>
+        <v>-5.190045599999999</v>
       </c>
       <c r="O23">
-        <v>-1.130835456</v>
+        <v>-1.660814592</v>
       </c>
       <c r="P23">
-        <v>-2.403025344</v>
+        <v>-3.529231008</v>
       </c>
       <c r="Q23">
-        <v>6.836974656</v>
+        <v>5.710768992</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1227029912931722</v>
+        <v>0.1240981841712958</v>
       </c>
       <c r="T23">
-        <v>1.002303778560177</v>
+        <v>1.020487818869253</v>
       </c>
       <c r="U23">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.1628054854772836</v>
+        <v>0.1323383011721431</v>
       </c>
       <c r="W23">
-        <v>0.1681086585161615</v>
+        <v>0.2045946285836087</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.5087671421165114</v>
+        <v>0.4135571911629473</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1418074019420046</v>
+        <v>0.1437074019420047</v>
       </c>
       <c r="C24">
-        <v>70.70508617464631</v>
+        <v>66.99779250485928</v>
       </c>
       <c r="D24">
-        <v>103.1270861746463</v>
+        <v>101.1257925048593</v>
       </c>
       <c r="E24">
-        <v>-0.3680000000000021</v>
+        <v>1.338000000000001</v>
       </c>
       <c r="F24">
-        <v>37.532</v>
+        <v>39.238</v>
       </c>
       <c r="G24">
         <v>5.11</v>
@@ -3255,37 +3255,37 @@
         <v>3.66</v>
       </c>
       <c r="M24">
-        <v>8.8500456</v>
+        <v>9.2523204</v>
       </c>
       <c r="N24">
-        <v>-5.190045599999999</v>
+        <v>-5.5923204</v>
       </c>
       <c r="O24">
-        <v>-1.660814592</v>
+        <v>-1.789542528</v>
       </c>
       <c r="P24">
-        <v>-3.529231008</v>
+        <v>-3.802777872</v>
       </c>
       <c r="Q24">
-        <v>5.710768992</v>
+        <v>5.437222128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1240981841712958</v>
+        <v>0.125115043705988</v>
       </c>
       <c r="T24">
-        <v>1.020487818869253</v>
+        <v>1.033740907425997</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.1323383011721431</v>
+        <v>0.1265844619907456</v>
       </c>
       <c r="W24">
-        <v>0.2045946285836087</v>
+        <v>0.2059513838625822</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.4135571911629473</v>
+        <v>0.3955764437210799</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1437074019420047</v>
+        <v>0.1456074019420046</v>
       </c>
       <c r="C25">
-        <v>66.99779250485928</v>
+        <v>63.36669474636959</v>
       </c>
       <c r="D25">
-        <v>101.1257925048593</v>
+        <v>99.20069474636959</v>
       </c>
       <c r="E25">
-        <v>1.338000000000001</v>
+        <v>3.044000000000004</v>
       </c>
       <c r="F25">
-        <v>39.238</v>
+        <v>40.944</v>
       </c>
       <c r="G25">
         <v>5.11</v>
@@ -3337,37 +3337,37 @@
         <v>3.66</v>
       </c>
       <c r="M25">
-        <v>9.2523204</v>
+        <v>9.654595200000001</v>
       </c>
       <c r="N25">
-        <v>-5.5923204</v>
+        <v>-5.994595200000001</v>
       </c>
       <c r="O25">
-        <v>-1.789542528</v>
+        <v>-1.918270464</v>
       </c>
       <c r="P25">
-        <v>-3.802777872</v>
+        <v>-4.076324736</v>
       </c>
       <c r="Q25">
-        <v>5.437222128</v>
+        <v>5.163675264</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.125115043705988</v>
+        <v>0.1261586627021194</v>
       </c>
       <c r="T25">
-        <v>1.033740907425997</v>
+        <v>1.047342761471075</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1265844619907456</v>
+        <v>0.1213101094077979</v>
       </c>
       <c r="W25">
-        <v>0.2059513838625822</v>
+        <v>0.2071950762016413</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3955764437210799</v>
+        <v>0.3790940918993683</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1456074019420046</v>
+        <v>0.1475074019420046</v>
       </c>
       <c r="C26">
-        <v>63.3666947463696</v>
+        <v>59.80752264267574</v>
       </c>
       <c r="D26">
-        <v>99.20069474636959</v>
+        <v>97.34752264267574</v>
       </c>
       <c r="E26">
-        <v>3.043999999999997</v>
+        <v>4.75</v>
       </c>
       <c r="F26">
-        <v>40.944</v>
+        <v>42.65</v>
       </c>
       <c r="G26">
         <v>5.11</v>
@@ -3419,37 +3419,37 @@
         <v>3.66</v>
       </c>
       <c r="M26">
-        <v>9.654595199999999</v>
+        <v>10.05687</v>
       </c>
       <c r="N26">
-        <v>-5.994595199999999</v>
+        <v>-6.39687</v>
       </c>
       <c r="O26">
-        <v>-1.918270464</v>
+        <v>-2.0469984</v>
       </c>
       <c r="P26">
-        <v>-4.076324735999999</v>
+        <v>-4.3498716</v>
       </c>
       <c r="Q26">
-        <v>5.163675264000001</v>
+        <v>4.8901284</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1261586627021194</v>
+        <v>0.1272301115381476</v>
       </c>
       <c r="T26">
-        <v>1.047342761471075</v>
+        <v>1.061307331624023</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.1213101094077979</v>
+        <v>0.1164577050314859</v>
       </c>
       <c r="W26">
-        <v>0.2071950762016413</v>
+        <v>0.2083392731535756</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3790940918993684</v>
+        <v>0.3639303282233936</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1475074019420046</v>
+        <v>0.1494074019420046</v>
       </c>
       <c r="C27">
-        <v>59.80752264267574</v>
+        <v>56.31631917695601</v>
       </c>
       <c r="D27">
-        <v>97.34752264267574</v>
+        <v>95.56231917695601</v>
       </c>
       <c r="E27">
-        <v>4.75</v>
+        <v>6.456000000000003</v>
       </c>
       <c r="F27">
-        <v>42.65</v>
+        <v>44.356</v>
       </c>
       <c r="G27">
         <v>5.11</v>
@@ -3501,37 +3501,37 @@
         <v>3.66</v>
       </c>
       <c r="M27">
-        <v>10.05687</v>
+        <v>10.4591448</v>
       </c>
       <c r="N27">
-        <v>-6.39687</v>
+        <v>-6.799144800000001</v>
       </c>
       <c r="O27">
-        <v>-2.0469984</v>
+        <v>-2.175726336</v>
       </c>
       <c r="P27">
-        <v>-4.3498716</v>
+        <v>-4.623418464</v>
       </c>
       <c r="Q27">
-        <v>4.8901284</v>
+        <v>4.616581536</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1272301115381476</v>
+        <v>0.1283305184508253</v>
       </c>
       <c r="T27">
-        <v>1.061307331624023</v>
+        <v>1.075649322591915</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1164577050314859</v>
+        <v>0.1119785625302749</v>
       </c>
       <c r="W27">
-        <v>0.2083392731535756</v>
+        <v>0.2093954549553612</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3639303282233936</v>
+        <v>0.3499330079071092</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1494074019420046</v>
+        <v>0.1513074019420046</v>
       </c>
       <c r="C28">
-        <v>56.31631917695601</v>
+        <v>52.8894123676307</v>
       </c>
       <c r="D28">
-        <v>95.56231917695601</v>
+        <v>93.84141236763071</v>
       </c>
       <c r="E28">
-        <v>6.456000000000003</v>
+        <v>8.162000000000006</v>
       </c>
       <c r="F28">
-        <v>44.356</v>
+        <v>46.062</v>
       </c>
       <c r="G28">
         <v>5.11</v>
@@ -3583,37 +3583,37 @@
         <v>3.66</v>
       </c>
       <c r="M28">
-        <v>10.4591448</v>
+        <v>10.8614196</v>
       </c>
       <c r="N28">
-        <v>-6.799144800000001</v>
+        <v>-7.201419600000001</v>
       </c>
       <c r="O28">
-        <v>-2.175726336</v>
+        <v>-2.304454272000001</v>
       </c>
       <c r="P28">
-        <v>-4.623418464</v>
+        <v>-4.896965328</v>
       </c>
       <c r="Q28">
-        <v>4.616581536</v>
+        <v>4.343034672</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1283305184508253</v>
+        <v>0.1294610734980969</v>
       </c>
       <c r="T28">
-        <v>1.075649322591915</v>
+        <v>1.090384244819202</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1119785625302749</v>
+        <v>0.107831208362487</v>
       </c>
       <c r="W28">
-        <v>0.2093954549553612</v>
+        <v>0.2103734010681256</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3499330079071092</v>
+        <v>0.3369725261327717</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1513074019420046</v>
+        <v>0.1532074019420047</v>
       </c>
       <c r="C29">
-        <v>52.8894123676307</v>
+        <v>49.52339005748513</v>
       </c>
       <c r="D29">
-        <v>93.84141236763071</v>
+        <v>92.18139005748513</v>
       </c>
       <c r="E29">
-        <v>8.162000000000006</v>
+        <v>9.868000000000002</v>
       </c>
       <c r="F29">
-        <v>46.062</v>
+        <v>47.768</v>
       </c>
       <c r="G29">
         <v>5.11</v>
@@ -3665,37 +3665,37 @@
         <v>3.66</v>
       </c>
       <c r="M29">
-        <v>10.8614196</v>
+        <v>11.2636944</v>
       </c>
       <c r="N29">
-        <v>-7.201419600000001</v>
+        <v>-7.6036944</v>
       </c>
       <c r="O29">
-        <v>-2.304454272000001</v>
+        <v>-2.433182208</v>
       </c>
       <c r="P29">
-        <v>-4.896965328</v>
+        <v>-5.170512192</v>
       </c>
       <c r="Q29">
-        <v>4.343034672</v>
+        <v>4.069487808</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1294610734980969</v>
+        <v>0.1306230328522371</v>
       </c>
       <c r="T29">
-        <v>1.090384244819202</v>
+        <v>1.105528470441691</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.107831208362487</v>
+        <v>0.1039800937781125</v>
       </c>
       <c r="W29">
-        <v>0.2103734010681256</v>
+        <v>0.2112814938871211</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3369725261327717</v>
+        <v>0.3249377930566014</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1532074019420047</v>
+        <v>0.1551074019420046</v>
       </c>
       <c r="C30">
-        <v>49.52339005748513</v>
+        <v>46.21507733211136</v>
       </c>
       <c r="D30">
-        <v>92.18139005748513</v>
+        <v>90.57907733211137</v>
       </c>
       <c r="E30">
-        <v>9.868000000000002</v>
+        <v>11.57400000000001</v>
       </c>
       <c r="F30">
-        <v>47.768</v>
+        <v>49.474</v>
       </c>
       <c r="G30">
         <v>5.11</v>
@@ -3747,37 +3747,37 @@
         <v>3.66</v>
       </c>
       <c r="M30">
-        <v>11.2636944</v>
+        <v>11.6659692</v>
       </c>
       <c r="N30">
-        <v>-7.6036944</v>
+        <v>-8.005969200000001</v>
       </c>
       <c r="O30">
-        <v>-2.433182208</v>
+        <v>-2.561910144</v>
       </c>
       <c r="P30">
-        <v>-5.170512192</v>
+        <v>-5.444059056</v>
       </c>
       <c r="Q30">
-        <v>4.069487808</v>
+        <v>3.795940944</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1306230328522371</v>
+        <v>0.1318177234557898</v>
       </c>
       <c r="T30">
-        <v>1.105528470441691</v>
+        <v>1.121099293969039</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1039800937781125</v>
+        <v>0.1003945733030051</v>
       </c>
       <c r="W30">
-        <v>0.2112814938871211</v>
+        <v>0.2121269596151514</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3249377930566014</v>
+        <v>0.313733041571891</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1551074019420046</v>
+        <v>0.1570074019420046</v>
       </c>
       <c r="C31">
-        <v>46.21507733211137</v>
+        <v>42.96151625321158</v>
       </c>
       <c r="D31">
-        <v>90.57907733211137</v>
+        <v>89.03151625321158</v>
       </c>
       <c r="E31">
-        <v>11.574</v>
+        <v>13.28</v>
       </c>
       <c r="F31">
-        <v>49.474</v>
+        <v>51.18</v>
       </c>
       <c r="G31">
         <v>5.11</v>
@@ -3829,37 +3829,37 @@
         <v>3.66</v>
       </c>
       <c r="M31">
-        <v>11.6659692</v>
+        <v>12.068244</v>
       </c>
       <c r="N31">
-        <v>-8.005969199999999</v>
+        <v>-8.408244</v>
       </c>
       <c r="O31">
-        <v>-2.561910144</v>
+        <v>-2.69063808</v>
       </c>
       <c r="P31">
-        <v>-5.444059056</v>
+        <v>-5.71760592</v>
       </c>
       <c r="Q31">
-        <v>3.795940944000001</v>
+        <v>3.52239408</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1318177234557898</v>
+        <v>0.1330465480765868</v>
       </c>
       <c r="T31">
-        <v>1.121099293969039</v>
+        <v>1.137114998168596</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1003945733030051</v>
+        <v>0.09704808752623828</v>
       </c>
       <c r="W31">
-        <v>0.2121269596151514</v>
+        <v>0.212916060961313</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3137330415718911</v>
+        <v>0.3032752735194947</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1570074019420046</v>
+        <v>0.1589074019420046</v>
       </c>
       <c r="C32">
-        <v>42.96151625321158</v>
+        <v>39.75994763456502</v>
       </c>
       <c r="D32">
-        <v>89.03151625321158</v>
+        <v>87.53594763456502</v>
       </c>
       <c r="E32">
-        <v>13.28</v>
+        <v>14.986</v>
       </c>
       <c r="F32">
-        <v>51.18</v>
+        <v>52.886</v>
       </c>
       <c r="G32">
         <v>5.11</v>
@@ -3911,37 +3911,37 @@
         <v>3.66</v>
       </c>
       <c r="M32">
-        <v>12.068244</v>
+        <v>12.4705188</v>
       </c>
       <c r="N32">
-        <v>-8.408244</v>
+        <v>-8.810518799999999</v>
       </c>
       <c r="O32">
-        <v>-2.69063808</v>
+        <v>-2.819366016</v>
       </c>
       <c r="P32">
-        <v>-5.71760592</v>
+        <v>-5.991152783999999</v>
       </c>
       <c r="Q32">
-        <v>3.52239408</v>
+        <v>3.248847216000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1330465480765868</v>
+        <v>0.1343109908023344</v>
       </c>
       <c r="T32">
-        <v>1.137114998168596</v>
+        <v>1.153594925678286</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.09704808752623828</v>
+        <v>0.09391750405764997</v>
       </c>
       <c r="W32">
-        <v>0.212916060961313</v>
+        <v>0.2136542525432061</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3032752735194947</v>
+        <v>0.2934922001801561</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1589074019420046</v>
+        <v>0.1608074019420046</v>
       </c>
       <c r="C33">
-        <v>39.75994763456502</v>
+        <v>36.60779462443494</v>
       </c>
       <c r="D33">
-        <v>87.53594763456502</v>
+        <v>86.08979462443494</v>
       </c>
       <c r="E33">
-        <v>14.986</v>
+        <v>16.692</v>
       </c>
       <c r="F33">
-        <v>52.886</v>
+        <v>54.592</v>
       </c>
       <c r="G33">
         <v>5.11</v>
@@ -3993,37 +3993,37 @@
         <v>3.66</v>
       </c>
       <c r="M33">
-        <v>12.4705188</v>
+        <v>12.8727936</v>
       </c>
       <c r="N33">
-        <v>-8.810518799999999</v>
+        <v>-9.212793599999999</v>
       </c>
       <c r="O33">
-        <v>-2.819366016</v>
+        <v>-2.948093952</v>
       </c>
       <c r="P33">
-        <v>-5.991152783999999</v>
+        <v>-6.264699648</v>
       </c>
       <c r="Q33">
-        <v>3.248847216000001</v>
+        <v>2.975300352000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1343109908023344</v>
+        <v>0.1356126230200158</v>
       </c>
       <c r="T33">
-        <v>1.153594925678286</v>
+        <v>1.170559556938261</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.09391750405764997</v>
+        <v>0.0909825820558484</v>
       </c>
       <c r="W33">
-        <v>0.2136542525432061</v>
+        <v>0.214346307151231</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2934922001801561</v>
+        <v>0.2843205689245263</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1608074019420046</v>
+        <v>0.1627074019420046</v>
       </c>
       <c r="C34">
-        <v>36.60779462443494</v>
+        <v>33.50264788890514</v>
       </c>
       <c r="D34">
-        <v>86.08979462443494</v>
+        <v>84.69064788890515</v>
       </c>
       <c r="E34">
-        <v>16.692</v>
+        <v>18.398</v>
       </c>
       <c r="F34">
-        <v>54.592</v>
+        <v>56.298</v>
       </c>
       <c r="G34">
         <v>5.11</v>
@@ -4075,37 +4075,37 @@
         <v>3.66</v>
       </c>
       <c r="M34">
-        <v>12.8727936</v>
+        <v>13.2750684</v>
       </c>
       <c r="N34">
-        <v>-9.212793599999999</v>
+        <v>-9.6150684</v>
       </c>
       <c r="O34">
-        <v>-2.948093952</v>
+        <v>-3.076821888</v>
       </c>
       <c r="P34">
-        <v>-6.264699648</v>
+        <v>-6.538246512000001</v>
       </c>
       <c r="Q34">
-        <v>2.975300352000001</v>
+        <v>2.701753488</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1356126230200158</v>
+        <v>0.1369531099307623</v>
       </c>
       <c r="T34">
-        <v>1.170559556938261</v>
+        <v>1.188030595101518</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0909825820558484</v>
+        <v>0.08822553411476207</v>
       </c>
       <c r="W34">
-        <v>0.214346307151231</v>
+        <v>0.2149964190557391</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2843205689245263</v>
+        <v>0.2757047941086315</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1627074019420046</v>
+        <v>0.1646074019420046</v>
       </c>
       <c r="C35">
-        <v>33.50264788890514</v>
+        <v>30.4422522169295</v>
       </c>
       <c r="D35">
-        <v>84.69064788890515</v>
+        <v>83.33625221692951</v>
       </c>
       <c r="E35">
-        <v>18.398</v>
+        <v>20.10400000000001</v>
       </c>
       <c r="F35">
-        <v>56.298</v>
+        <v>58.004</v>
       </c>
       <c r="G35">
         <v>5.11</v>
@@ -4157,37 +4157,37 @@
         <v>3.66</v>
       </c>
       <c r="M35">
-        <v>13.2750684</v>
+        <v>13.6773432</v>
       </c>
       <c r="N35">
-        <v>-9.6150684</v>
+        <v>-10.0173432</v>
       </c>
       <c r="O35">
-        <v>-3.076821888</v>
+        <v>-3.205549824</v>
       </c>
       <c r="P35">
-        <v>-6.538246512000001</v>
+        <v>-6.811793376000001</v>
       </c>
       <c r="Q35">
-        <v>2.701753488</v>
+        <v>2.428206624</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1369531099307623</v>
+        <v>0.138334217656986</v>
       </c>
       <c r="T35">
-        <v>1.188030595101518</v>
+        <v>1.206031058663663</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08822553411476207</v>
+        <v>0.0856306654643279</v>
       </c>
       <c r="W35">
-        <v>0.2149964190557391</v>
+        <v>0.2156082890835115</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2757047941086315</v>
+        <v>0.2675958295760247</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1646074019420046</v>
+        <v>0.1665074019420046</v>
       </c>
       <c r="C36">
-        <v>30.4422522169295</v>
+        <v>27.4244943904439</v>
       </c>
       <c r="D36">
-        <v>83.33625221692951</v>
+        <v>82.02449439044391</v>
       </c>
       <c r="E36">
-        <v>20.10400000000001</v>
+        <v>21.81</v>
       </c>
       <c r="F36">
-        <v>58.004</v>
+        <v>59.71</v>
       </c>
       <c r="G36">
         <v>5.11</v>
@@ -4239,37 +4239,37 @@
         <v>3.66</v>
       </c>
       <c r="M36">
-        <v>13.6773432</v>
+        <v>14.079618</v>
       </c>
       <c r="N36">
-        <v>-10.0173432</v>
+        <v>-10.419618</v>
       </c>
       <c r="O36">
-        <v>-3.205549824</v>
+        <v>-3.33427776</v>
       </c>
       <c r="P36">
-        <v>-6.811793376000001</v>
+        <v>-7.08534024</v>
       </c>
       <c r="Q36">
-        <v>2.428206624</v>
+        <v>2.15465976</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.138334217656986</v>
+        <v>0.139757821005555</v>
       </c>
       <c r="T36">
-        <v>1.206031058663663</v>
+        <v>1.224585382643104</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0856306654643279</v>
+        <v>0.08318407502248996</v>
       </c>
       <c r="W36">
-        <v>0.2156082890835115</v>
+        <v>0.2161851951096969</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2675958295760247</v>
+        <v>0.2599502344452811</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1665074019420046</v>
+        <v>0.1684074019420047</v>
       </c>
       <c r="C37">
-        <v>27.4244943904439</v>
+        <v>24.44739218231162</v>
       </c>
       <c r="D37">
-        <v>82.02449439044391</v>
+        <v>80.75339218231163</v>
       </c>
       <c r="E37">
-        <v>21.81</v>
+        <v>23.51600000000001</v>
       </c>
       <c r="F37">
-        <v>59.71</v>
+        <v>61.416</v>
       </c>
       <c r="G37">
         <v>5.11</v>
@@ -4321,37 +4321,37 @@
         <v>3.66</v>
       </c>
       <c r="M37">
-        <v>14.079618</v>
+        <v>14.4818928</v>
       </c>
       <c r="N37">
-        <v>-10.419618</v>
+        <v>-10.8218928</v>
       </c>
       <c r="O37">
-        <v>-3.33427776</v>
+        <v>-3.463005696</v>
       </c>
       <c r="P37">
-        <v>-7.08534024</v>
+        <v>-7.358887104000001</v>
       </c>
       <c r="Q37">
-        <v>2.15465976</v>
+        <v>1.881112895999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.139757821005555</v>
+        <v>0.1412259119587668</v>
       </c>
       <c r="T37">
-        <v>1.224585382643104</v>
+        <v>1.243719529246902</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.08318407502248996</v>
+        <v>0.08087340627186525</v>
       </c>
       <c r="W37">
-        <v>0.2161851951096969</v>
+        <v>0.2167300508010942</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2599502344452811</v>
+        <v>0.2527293945995789</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1684074019420047</v>
+        <v>0.1703074019420046</v>
       </c>
       <c r="C38">
-        <v>24.44739218231163</v>
+        <v>21.50908436162592</v>
       </c>
       <c r="D38">
-        <v>80.75339218231163</v>
+        <v>79.52108436162592</v>
       </c>
       <c r="E38">
-        <v>23.516</v>
+        <v>25.222</v>
       </c>
       <c r="F38">
-        <v>61.416</v>
+        <v>63.122</v>
       </c>
       <c r="G38">
         <v>5.11</v>
@@ -4403,37 +4403,37 @@
         <v>3.66</v>
       </c>
       <c r="M38">
-        <v>14.4818928</v>
+        <v>14.8841676</v>
       </c>
       <c r="N38">
-        <v>-10.8218928</v>
+        <v>-11.2241676</v>
       </c>
       <c r="O38">
-        <v>-3.463005696</v>
+        <v>-3.591733632</v>
       </c>
       <c r="P38">
-        <v>-7.358887104000001</v>
+        <v>-7.632433968000001</v>
       </c>
       <c r="Q38">
-        <v>1.881112895999999</v>
+        <v>1.607566031999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1412259119587668</v>
+        <v>0.1427406089739853</v>
       </c>
       <c r="T38">
-        <v>1.243719529246902</v>
+        <v>1.263461109076218</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08087340627186525</v>
+        <v>0.0786876385347878</v>
       </c>
       <c r="W38">
-        <v>0.2167300508010942</v>
+        <v>0.2172454548334971</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2527293945995789</v>
+        <v>0.2458988704212118</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1703074019420046</v>
+        <v>0.1722074019420047</v>
       </c>
       <c r="C39">
-        <v>21.50908436162592</v>
+        <v>18.60782160038026</v>
       </c>
       <c r="D39">
-        <v>79.52108436162592</v>
+        <v>78.32582160038027</v>
       </c>
       <c r="E39">
-        <v>25.222</v>
+        <v>26.928</v>
       </c>
       <c r="F39">
-        <v>63.122</v>
+        <v>64.828</v>
       </c>
       <c r="G39">
         <v>5.11</v>
@@ -4485,37 +4485,37 @@
         <v>3.66</v>
       </c>
       <c r="M39">
-        <v>14.8841676</v>
+        <v>15.2864424</v>
       </c>
       <c r="N39">
-        <v>-11.2241676</v>
+        <v>-11.6264424</v>
       </c>
       <c r="O39">
-        <v>-3.591733632</v>
+        <v>-3.720461568000001</v>
       </c>
       <c r="P39">
-        <v>-7.632433968000001</v>
+        <v>-7.905980832000001</v>
       </c>
       <c r="Q39">
-        <v>1.607566031999999</v>
+        <v>1.334019167999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1427406089739853</v>
+        <v>0.1443041671832431</v>
       </c>
       <c r="T39">
-        <v>1.263461109076218</v>
+        <v>1.283839514061318</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0786876385347878</v>
+        <v>0.07661691120492496</v>
       </c>
       <c r="W39">
-        <v>0.2172454548334971</v>
+        <v>0.2177337323378787</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2458988704212118</v>
+        <v>0.2394278475153905</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1722074019420047</v>
+        <v>0.1741074019420046</v>
       </c>
       <c r="C40">
-        <v>18.60782160038026</v>
+        <v>15.74195818807308</v>
       </c>
       <c r="D40">
-        <v>78.32582160038027</v>
+        <v>77.16595818807309</v>
       </c>
       <c r="E40">
-        <v>26.928</v>
+        <v>28.63400000000001</v>
       </c>
       <c r="F40">
-        <v>64.828</v>
+        <v>66.53400000000001</v>
       </c>
       <c r="G40">
         <v>5.11</v>
@@ -4567,37 +4567,37 @@
         <v>3.66</v>
       </c>
       <c r="M40">
-        <v>15.2864424</v>
+        <v>15.6887172</v>
       </c>
       <c r="N40">
-        <v>-11.6264424</v>
+        <v>-12.0287172</v>
       </c>
       <c r="O40">
-        <v>-3.720461568000001</v>
+        <v>-3.849189504000001</v>
       </c>
       <c r="P40">
-        <v>-7.905980832000001</v>
+        <v>-8.179527696000001</v>
       </c>
       <c r="Q40">
-        <v>1.334019167999999</v>
+        <v>1.060472303999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1443041671832431</v>
+        <v>0.1459189895960832</v>
       </c>
       <c r="T40">
-        <v>1.283839514061318</v>
+        <v>1.30488606347216</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07661691120492496</v>
+        <v>0.07465237502018328</v>
       </c>
       <c r="W40">
-        <v>0.2177337323378787</v>
+        <v>0.2181969699702408</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2394278475153905</v>
+        <v>0.2332886719380728</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1741074019420046</v>
+        <v>0.1760074019420046</v>
       </c>
       <c r="C41">
-        <v>15.74195818807308</v>
+        <v>12.90994447172044</v>
       </c>
       <c r="D41">
-        <v>77.16595818807309</v>
+        <v>76.03994447172043</v>
       </c>
       <c r="E41">
-        <v>28.63400000000001</v>
+        <v>30.34</v>
       </c>
       <c r="F41">
-        <v>66.53400000000001</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="G41">
         <v>5.11</v>
@@ -4649,37 +4649,37 @@
         <v>3.66</v>
       </c>
       <c r="M41">
-        <v>15.6887172</v>
+        <v>16.090992</v>
       </c>
       <c r="N41">
-        <v>-12.0287172</v>
+        <v>-12.430992</v>
       </c>
       <c r="O41">
-        <v>-3.849189504000001</v>
+        <v>-3.97791744</v>
       </c>
       <c r="P41">
-        <v>-8.179527696000001</v>
+        <v>-8.453074559999999</v>
       </c>
       <c r="Q41">
-        <v>1.060472303999999</v>
+        <v>0.786925440000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1459189895960832</v>
+        <v>0.1475876394226846</v>
       </c>
       <c r="T41">
-        <v>1.30488606347216</v>
+        <v>1.326634164530029</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07465237502018328</v>
+        <v>0.07278606564467871</v>
       </c>
       <c r="W41">
-        <v>0.2181969699702408</v>
+        <v>0.2186370457209848</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2332886719380728</v>
+        <v>0.227456455139621</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1760074019420046</v>
+        <v>0.1779074019420047</v>
       </c>
       <c r="C42">
-        <v>12.90994447172044</v>
+        <v>10.110319948246</v>
       </c>
       <c r="D42">
-        <v>76.03994447172043</v>
+        <v>74.946319948246</v>
       </c>
       <c r="E42">
-        <v>30.34</v>
+        <v>32.046</v>
       </c>
       <c r="F42">
-        <v>68.23999999999999</v>
+        <v>69.946</v>
       </c>
       <c r="G42">
         <v>5.11</v>
@@ -4731,37 +4731,37 @@
         <v>3.66</v>
       </c>
       <c r="M42">
-        <v>16.090992</v>
+        <v>16.4932668</v>
       </c>
       <c r="N42">
-        <v>-12.430992</v>
+        <v>-12.8332668</v>
       </c>
       <c r="O42">
-        <v>-3.97791744</v>
+        <v>-4.106645376</v>
       </c>
       <c r="P42">
-        <v>-8.453074559999999</v>
+        <v>-8.726621424000001</v>
       </c>
       <c r="Q42">
-        <v>0.786925440000001</v>
+        <v>0.5133785759999991</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1475876394226846</v>
+        <v>0.1493128536501877</v>
       </c>
       <c r="T42">
-        <v>1.326634164530029</v>
+        <v>1.349119489352572</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07278606564467871</v>
+        <v>0.07101079575090606</v>
       </c>
       <c r="W42">
-        <v>0.2186370457209848</v>
+        <v>0.2190556543619364</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.227456455139621</v>
+        <v>0.2219087367215814</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1779074019420047</v>
+        <v>0.1798074019420046</v>
       </c>
       <c r="C43">
-        <v>10.110319948246</v>
+        <v>7.34170694450097</v>
       </c>
       <c r="D43">
-        <v>74.946319948246</v>
+        <v>73.88370694450097</v>
       </c>
       <c r="E43">
-        <v>32.046</v>
+        <v>33.752</v>
       </c>
       <c r="F43">
-        <v>69.946</v>
+        <v>71.652</v>
       </c>
       <c r="G43">
         <v>5.11</v>
@@ -4813,37 +4813,37 @@
         <v>3.66</v>
       </c>
       <c r="M43">
-        <v>16.4932668</v>
+        <v>16.8955416</v>
       </c>
       <c r="N43">
-        <v>-12.8332668</v>
+        <v>-13.2355416</v>
       </c>
       <c r="O43">
-        <v>-4.106645376</v>
+        <v>-4.235373312</v>
       </c>
       <c r="P43">
-        <v>-8.726621424000001</v>
+        <v>-9.000168288000001</v>
       </c>
       <c r="Q43">
-        <v>0.5133785759999991</v>
+        <v>0.2398317119999991</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1493128536501877</v>
+        <v>0.1510975580234668</v>
       </c>
       <c r="T43">
-        <v>1.349119489352572</v>
+        <v>1.372380170203478</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07101079575090606</v>
+        <v>0.06932006251874163</v>
       </c>
       <c r="W43">
-        <v>0.2190556543619364</v>
+        <v>0.2194543292580807</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2219087367215814</v>
+        <v>0.2166251953710676</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1798074019420046</v>
+        <v>0.1817074019420046</v>
       </c>
       <c r="C44">
-        <v>7.341706944500942</v>
+        <v>4.602804827407624</v>
       </c>
       <c r="D44">
-        <v>73.88370694450094</v>
+        <v>72.85080482740761</v>
       </c>
       <c r="E44">
-        <v>33.752</v>
+        <v>35.45799999999999</v>
       </c>
       <c r="F44">
-        <v>71.652</v>
+        <v>73.35799999999999</v>
       </c>
       <c r="G44">
         <v>5.11</v>
@@ -4895,37 +4895,37 @@
         <v>3.66</v>
       </c>
       <c r="M44">
-        <v>16.8955416</v>
+        <v>17.2978164</v>
       </c>
       <c r="N44">
-        <v>-13.2355416</v>
+        <v>-13.6378164</v>
       </c>
       <c r="O44">
-        <v>-4.235373312</v>
+        <v>-4.364101248</v>
       </c>
       <c r="P44">
-        <v>-9.000168288000001</v>
+        <v>-9.273715151999998</v>
       </c>
       <c r="Q44">
-        <v>0.2398317119999991</v>
+        <v>-0.03371515199999742</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1510975580234668</v>
+        <v>0.1529448836028258</v>
       </c>
       <c r="T44">
-        <v>1.372380170203478</v>
+        <v>1.396457015294767</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06932006251874163</v>
+        <v>0.06770796804156161</v>
       </c>
       <c r="W44">
-        <v>0.2194543292580807</v>
+        <v>0.2198344611357998</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2166251953710676</v>
+        <v>0.21158740012988</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1817074019420046</v>
+        <v>0.1836074019420046</v>
       </c>
       <c r="C45">
-        <v>4.602804827407624</v>
+        <v>1.892384693064429</v>
       </c>
       <c r="D45">
-        <v>72.85080482740761</v>
+        <v>71.84638469306442</v>
       </c>
       <c r="E45">
-        <v>35.45799999999999</v>
+        <v>37.16399999999999</v>
       </c>
       <c r="F45">
-        <v>73.35799999999999</v>
+        <v>75.06399999999999</v>
       </c>
       <c r="G45">
         <v>5.11</v>
@@ -4977,37 +4977,37 @@
         <v>3.66</v>
       </c>
       <c r="M45">
-        <v>17.2978164</v>
+        <v>17.7000912</v>
       </c>
       <c r="N45">
-        <v>-13.6378164</v>
+        <v>-14.0400912</v>
       </c>
       <c r="O45">
-        <v>-4.364101248</v>
+        <v>-4.492829184</v>
       </c>
       <c r="P45">
-        <v>-9.273715151999998</v>
+        <v>-9.547262015999999</v>
       </c>
       <c r="Q45">
-        <v>-0.03371515199999742</v>
+        <v>-0.3072620159999992</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1529448836028258</v>
+        <v>0.1548581850957335</v>
       </c>
       <c r="T45">
-        <v>1.396457015294767</v>
+        <v>1.421393747710745</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06770796804156161</v>
+        <v>0.06616915058607156</v>
       </c>
       <c r="W45">
-        <v>0.2198344611357998</v>
+        <v>0.2201973142918043</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.21158740012988</v>
+        <v>0.2067785955814736</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1836074019420046</v>
+        <v>0.1855074019420047</v>
       </c>
       <c r="C46">
-        <v>1.892384693064429</v>
+        <v>-0.7907155107851196</v>
       </c>
       <c r="D46">
-        <v>71.84638469306442</v>
+        <v>70.86928448921488</v>
       </c>
       <c r="E46">
-        <v>37.16399999999999</v>
+        <v>38.87</v>
       </c>
       <c r="F46">
-        <v>75.06399999999999</v>
+        <v>76.77</v>
       </c>
       <c r="G46">
         <v>5.11</v>
@@ -5059,37 +5059,37 @@
         <v>3.66</v>
       </c>
       <c r="M46">
-        <v>17.7000912</v>
+        <v>18.102366</v>
       </c>
       <c r="N46">
-        <v>-14.0400912</v>
+        <v>-14.442366</v>
       </c>
       <c r="O46">
-        <v>-4.492829184</v>
+        <v>-4.62155712</v>
       </c>
       <c r="P46">
-        <v>-9.547262015999999</v>
+        <v>-9.82080888</v>
       </c>
       <c r="Q46">
-        <v>-0.3072620159999992</v>
+        <v>-0.5808088799999993</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1548581850957335</v>
+        <v>0.1568410611883832</v>
       </c>
       <c r="T46">
-        <v>1.421393747710745</v>
+        <v>1.447237270396395</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06616915058607156</v>
+        <v>0.06469872501749219</v>
       </c>
       <c r="W46">
-        <v>0.2201973142918043</v>
+        <v>0.2205440406408753</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2067785955814736</v>
+        <v>0.2021835156796631</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1855074019420047</v>
+        <v>0.1874074019420047</v>
       </c>
       <c r="C47">
-        <v>-0.7907155107851196</v>
+        <v>-3.447595469621291</v>
       </c>
       <c r="D47">
-        <v>70.86928448921488</v>
+        <v>69.91840453037871</v>
       </c>
       <c r="E47">
-        <v>38.87</v>
+        <v>40.576</v>
       </c>
       <c r="F47">
-        <v>76.77</v>
+        <v>78.476</v>
       </c>
       <c r="G47">
         <v>5.11</v>
@@ -5141,37 +5141,37 @@
         <v>3.66</v>
       </c>
       <c r="M47">
-        <v>18.102366</v>
+        <v>18.5046408</v>
       </c>
       <c r="N47">
-        <v>-14.442366</v>
+        <v>-14.8446408</v>
       </c>
       <c r="O47">
-        <v>-4.62155712</v>
+        <v>-4.750285056</v>
       </c>
       <c r="P47">
-        <v>-9.82080888</v>
+        <v>-10.094355744</v>
       </c>
       <c r="Q47">
-        <v>-0.5808088799999993</v>
+        <v>-0.8543557440000011</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1568410611883832</v>
+        <v>0.1588973771363162</v>
       </c>
       <c r="T47">
-        <v>1.447237270396395</v>
+        <v>1.474037960588921</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06469872501749219</v>
+        <v>0.0632922309953728</v>
       </c>
       <c r="W47">
-        <v>0.2205440406408753</v>
+        <v>0.2208756919312911</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2021835156796631</v>
+        <v>0.19778822186054</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1874074019420047</v>
+        <v>0.1893074019420047</v>
       </c>
       <c r="C48">
-        <v>-3.447595469621291</v>
+        <v>-6.0792966307461</v>
       </c>
       <c r="D48">
-        <v>69.91840453037871</v>
+        <v>68.9927033692539</v>
       </c>
       <c r="E48">
-        <v>40.576</v>
+        <v>42.282</v>
       </c>
       <c r="F48">
-        <v>78.476</v>
+        <v>80.182</v>
       </c>
       <c r="G48">
         <v>5.11</v>
@@ -5223,37 +5223,37 @@
         <v>3.66</v>
       </c>
       <c r="M48">
-        <v>18.5046408</v>
+        <v>18.9069156</v>
       </c>
       <c r="N48">
-        <v>-14.8446408</v>
+        <v>-15.2469156</v>
       </c>
       <c r="O48">
-        <v>-4.750285056</v>
+        <v>-4.879012992000001</v>
       </c>
       <c r="P48">
-        <v>-10.094355744</v>
+        <v>-10.367902608</v>
       </c>
       <c r="Q48">
-        <v>-0.8543557440000011</v>
+        <v>-1.127902608000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1588973771363162</v>
+        <v>0.1610312899124731</v>
       </c>
       <c r="T48">
-        <v>1.474037960588921</v>
+        <v>1.501849997581165</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0632922309953728</v>
+        <v>0.06194558778270529</v>
       </c>
       <c r="W48">
-        <v>0.2208756919312911</v>
+        <v>0.2211932304008381</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.19778822186054</v>
+        <v>0.193579961820954</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1893074019420047</v>
+        <v>0.1912074019420047</v>
       </c>
       <c r="C49">
-        <v>-6.0792966307461</v>
+        <v>-8.686806008197664</v>
       </c>
       <c r="D49">
-        <v>68.9927033692539</v>
+        <v>68.09119399180234</v>
       </c>
       <c r="E49">
-        <v>42.282</v>
+        <v>43.98800000000001</v>
       </c>
       <c r="F49">
-        <v>80.182</v>
+        <v>81.88800000000001</v>
       </c>
       <c r="G49">
         <v>5.11</v>
@@ -5305,37 +5305,37 @@
         <v>3.66</v>
       </c>
       <c r="M49">
-        <v>18.9069156</v>
+        <v>19.3091904</v>
       </c>
       <c r="N49">
-        <v>-15.2469156</v>
+        <v>-15.6491904</v>
       </c>
       <c r="O49">
-        <v>-4.879012992000001</v>
+        <v>-5.007740928</v>
       </c>
       <c r="P49">
-        <v>-10.367902608</v>
+        <v>-10.641449472</v>
       </c>
       <c r="Q49">
-        <v>-1.127902608000001</v>
+        <v>-1.401449472000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1610312899124731</v>
+        <v>0.1632472762569437</v>
       </c>
       <c r="T49">
-        <v>1.501849997581165</v>
+        <v>1.530731728303879</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06194558778270529</v>
+        <v>0.06065505470389893</v>
       </c>
       <c r="W49">
-        <v>0.2211932304008381</v>
+        <v>0.2214975381008207</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.193579961820954</v>
+        <v>0.1895470459496841</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1912074019420046</v>
+        <v>0.1931074019420047</v>
       </c>
       <c r="C50">
-        <v>-8.686806008197635</v>
+        <v>-11.27105969320499</v>
       </c>
       <c r="D50">
-        <v>68.09119399180236</v>
+        <v>67.21294030679501</v>
       </c>
       <c r="E50">
-        <v>43.98799999999999</v>
+        <v>45.694</v>
       </c>
       <c r="F50">
-        <v>81.88799999999999</v>
+        <v>83.59399999999999</v>
       </c>
       <c r="G50">
         <v>5.11</v>
@@ -5387,37 +5387,37 @@
         <v>3.66</v>
       </c>
       <c r="M50">
-        <v>19.3091904</v>
+        <v>19.7114652</v>
       </c>
       <c r="N50">
-        <v>-15.6491904</v>
+        <v>-16.0514652</v>
       </c>
       <c r="O50">
-        <v>-5.007740928</v>
+        <v>-5.136468864</v>
       </c>
       <c r="P50">
-        <v>-10.641449472</v>
+        <v>-10.914996336</v>
       </c>
       <c r="Q50">
-        <v>-1.401449471999998</v>
+        <v>-1.674996335999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1632472762569437</v>
+        <v>0.1655501640266877</v>
       </c>
       <c r="T50">
-        <v>1.530731728303879</v>
+        <v>1.560746075917681</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06065505470389893</v>
+        <v>0.05941719644463569</v>
       </c>
       <c r="W50">
-        <v>0.2214975381008206</v>
+        <v>0.2217894250783549</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1895470459496842</v>
+        <v>0.1856787388894865</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1931074019420047</v>
+        <v>0.1950074019420047</v>
       </c>
       <c r="C51">
-        <v>-11.27105969320499</v>
+        <v>-13.83294609643147</v>
       </c>
       <c r="D51">
-        <v>67.21294030679501</v>
+        <v>66.35705390356853</v>
       </c>
       <c r="E51">
-        <v>45.694</v>
+        <v>47.4</v>
       </c>
       <c r="F51">
-        <v>83.59399999999999</v>
+        <v>85.3</v>
       </c>
       <c r="G51">
         <v>5.11</v>
@@ -5469,37 +5469,37 @@
         <v>3.66</v>
       </c>
       <c r="M51">
-        <v>19.7114652</v>
+        <v>20.11374</v>
       </c>
       <c r="N51">
-        <v>-16.0514652</v>
+        <v>-16.45374</v>
       </c>
       <c r="O51">
-        <v>-5.136468864</v>
+        <v>-5.2651968</v>
       </c>
       <c r="P51">
-        <v>-10.914996336</v>
+        <v>-11.1885432</v>
       </c>
       <c r="Q51">
-        <v>-1.674996335999998</v>
+        <v>-1.9485432</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1655501640266877</v>
+        <v>0.1679451673072215</v>
       </c>
       <c r="T51">
-        <v>1.560746075917681</v>
+        <v>1.591960997436035</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05941719644463569</v>
+        <v>0.05822885251574297</v>
       </c>
       <c r="W51">
-        <v>0.2217894250783549</v>
+        <v>0.2220696365767878</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1856787388894865</v>
+        <v>0.1819651641116968</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1950074019420047</v>
+        <v>0.1969074019420047</v>
       </c>
       <c r="C52">
-        <v>-13.83294609643147</v>
+        <v>-16.3733089456132</v>
       </c>
       <c r="D52">
-        <v>66.35705390356853</v>
+        <v>65.5226910543868</v>
       </c>
       <c r="E52">
-        <v>47.4</v>
+        <v>49.106</v>
       </c>
       <c r="F52">
-        <v>85.3</v>
+        <v>87.006</v>
       </c>
       <c r="G52">
         <v>5.11</v>
@@ -5551,37 +5551,37 @@
         <v>3.66</v>
       </c>
       <c r="M52">
-        <v>20.11374</v>
+        <v>20.5160148</v>
       </c>
       <c r="N52">
-        <v>-16.45374</v>
+        <v>-16.8560148</v>
       </c>
       <c r="O52">
-        <v>-5.2651968</v>
+        <v>-5.393924736000001</v>
       </c>
       <c r="P52">
-        <v>-11.1885432</v>
+        <v>-11.462090064</v>
       </c>
       <c r="Q52">
-        <v>-1.9485432</v>
+        <v>-2.222090064</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1679451673072215</v>
+        <v>0.1704379258236954</v>
       </c>
       <c r="T52">
-        <v>1.591960997436035</v>
+        <v>1.624449997383709</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05822885251574297</v>
+        <v>0.05708711030955194</v>
       </c>
       <c r="W52">
-        <v>0.2220696365767878</v>
+        <v>0.2223388593890077</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1819651641116968</v>
+        <v>0.1783972197173498</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1969074019420047</v>
+        <v>0.1988074019420047</v>
       </c>
       <c r="C53">
-        <v>-16.3733089456132</v>
+        <v>-18.892950059855</v>
       </c>
       <c r="D53">
-        <v>65.5226910543868</v>
+        <v>64.70904994014501</v>
       </c>
       <c r="E53">
-        <v>49.106</v>
+        <v>50.812</v>
       </c>
       <c r="F53">
-        <v>87.006</v>
+        <v>88.712</v>
       </c>
       <c r="G53">
         <v>5.11</v>
@@ -5633,37 +5633,37 @@
         <v>3.66</v>
       </c>
       <c r="M53">
-        <v>20.5160148</v>
+        <v>20.9182896</v>
       </c>
       <c r="N53">
-        <v>-16.8560148</v>
+        <v>-17.2582896</v>
       </c>
       <c r="O53">
-        <v>-5.393924736000001</v>
+        <v>-5.522652672</v>
       </c>
       <c r="P53">
-        <v>-11.462090064</v>
+        <v>-11.735636928</v>
       </c>
       <c r="Q53">
-        <v>-2.222090064</v>
+        <v>-2.495636928000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1704379258236954</v>
+        <v>0.1730345492783557</v>
       </c>
       <c r="T53">
-        <v>1.624449997383709</v>
+        <v>1.658292705662536</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05708711030955194</v>
+        <v>0.05598928126513747</v>
       </c>
       <c r="W53">
-        <v>0.2223388593890077</v>
+        <v>0.2225977274776806</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1783972197173498</v>
+        <v>0.1749665039535546</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1988074019420047</v>
+        <v>0.2007074019420046</v>
       </c>
       <c r="C54">
-        <v>-18.892950059855</v>
+        <v>-21.39263191975932</v>
       </c>
       <c r="D54">
-        <v>64.70904994014501</v>
+        <v>63.91536808024068</v>
       </c>
       <c r="E54">
-        <v>50.812</v>
+        <v>52.51800000000001</v>
       </c>
       <c r="F54">
-        <v>88.712</v>
+        <v>90.41800000000001</v>
       </c>
       <c r="G54">
         <v>5.11</v>
@@ -5715,37 +5715,37 @@
         <v>3.66</v>
       </c>
       <c r="M54">
-        <v>20.9182896</v>
+        <v>21.3205644</v>
       </c>
       <c r="N54">
-        <v>-17.2582896</v>
+        <v>-17.6605644</v>
       </c>
       <c r="O54">
-        <v>-5.522652672</v>
+        <v>-5.651380608000001</v>
       </c>
       <c r="P54">
-        <v>-11.735636928</v>
+        <v>-12.009183792</v>
       </c>
       <c r="Q54">
-        <v>-2.495636928000001</v>
+        <v>-2.769183792000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1730345492783557</v>
+        <v>0.175741667348108</v>
       </c>
       <c r="T54">
-        <v>1.658292705662536</v>
+        <v>1.693575529187271</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05598928126513747</v>
+        <v>0.05493287973183299</v>
       </c>
       <c r="W54">
-        <v>0.2225977274776806</v>
+        <v>0.2228468269592338</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1749665039535546</v>
+        <v>0.1716652491619781</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2007074019420046</v>
+        <v>0.2026074019420046</v>
       </c>
       <c r="C55">
-        <v>-21.39263191975932</v>
+        <v>-23.87308005070514</v>
       </c>
       <c r="D55">
-        <v>63.91536808024068</v>
+        <v>63.14091994929486</v>
       </c>
       <c r="E55">
-        <v>52.51800000000001</v>
+        <v>54.22400000000001</v>
       </c>
       <c r="F55">
-        <v>90.41800000000001</v>
+        <v>92.12400000000001</v>
       </c>
       <c r="G55">
         <v>5.11</v>
@@ -5797,37 +5797,37 @@
         <v>3.66</v>
       </c>
       <c r="M55">
-        <v>21.3205644</v>
+        <v>21.7228392</v>
       </c>
       <c r="N55">
-        <v>-17.6605644</v>
+        <v>-18.0628392</v>
       </c>
       <c r="O55">
-        <v>-5.651380608000001</v>
+        <v>-5.780108544000001</v>
       </c>
       <c r="P55">
-        <v>-12.009183792</v>
+        <v>-12.282730656</v>
       </c>
       <c r="Q55">
-        <v>-2.769183792000002</v>
+        <v>-3.042730656000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.175741667348108</v>
+        <v>0.1785664862035016</v>
       </c>
       <c r="T55">
-        <v>1.693575529187271</v>
+        <v>1.730392388517429</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05493287973183299</v>
+        <v>0.05391560418124348</v>
       </c>
       <c r="W55">
-        <v>0.2228468269592338</v>
+        <v>0.2230867005340628</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1716652491619781</v>
+        <v>0.1684862630663859</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2026074019420046</v>
+        <v>0.2045074019420046</v>
       </c>
       <c r="C56">
-        <v>-23.87308005070514</v>
+        <v>-26.3349852349353</v>
       </c>
       <c r="D56">
-        <v>63.14091994929486</v>
+        <v>62.3850147650647</v>
       </c>
       <c r="E56">
-        <v>54.22400000000001</v>
+        <v>55.93</v>
       </c>
       <c r="F56">
-        <v>92.12400000000001</v>
+        <v>93.83</v>
       </c>
       <c r="G56">
         <v>5.11</v>
@@ -5879,37 +5879,37 @@
         <v>3.66</v>
       </c>
       <c r="M56">
-        <v>21.7228392</v>
+        <v>22.125114</v>
       </c>
       <c r="N56">
-        <v>-18.0628392</v>
+        <v>-18.465114</v>
       </c>
       <c r="O56">
-        <v>-5.780108544000001</v>
+        <v>-5.90883648</v>
       </c>
       <c r="P56">
-        <v>-12.282730656</v>
+        <v>-12.55627752</v>
       </c>
       <c r="Q56">
-        <v>-3.042730656000002</v>
+        <v>-3.31627752</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1785664862035016</v>
+        <v>0.1815168525635794</v>
       </c>
       <c r="T56">
-        <v>1.730392388517429</v>
+        <v>1.768845552706705</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05391560418124348</v>
+        <v>0.05293532046885725</v>
       </c>
       <c r="W56">
-        <v>0.2230867005340628</v>
+        <v>0.2233178514334435</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1684862630663859</v>
+        <v>0.1654228764651789</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2045074019420046</v>
+        <v>0.2064074019420047</v>
       </c>
       <c r="C57">
-        <v>-26.3349852349353</v>
+        <v>-28.7790055666285</v>
       </c>
       <c r="D57">
-        <v>62.3850147650647</v>
+        <v>61.6469944333715</v>
       </c>
       <c r="E57">
-        <v>55.93</v>
+        <v>57.636</v>
       </c>
       <c r="F57">
-        <v>93.83</v>
+        <v>95.536</v>
       </c>
       <c r="G57">
         <v>5.11</v>
@@ -5961,37 +5961,37 @@
         <v>3.66</v>
       </c>
       <c r="M57">
-        <v>22.125114</v>
+        <v>22.5273888</v>
       </c>
       <c r="N57">
-        <v>-18.465114</v>
+        <v>-18.8673888</v>
       </c>
       <c r="O57">
-        <v>-5.90883648</v>
+        <v>-6.037564416</v>
       </c>
       <c r="P57">
-        <v>-12.55627752</v>
+        <v>-12.829824384</v>
       </c>
       <c r="Q57">
-        <v>-3.31627752</v>
+        <v>-3.589824384</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1815168525635794</v>
+        <v>0.184601326485479</v>
       </c>
       <c r="T57">
-        <v>1.768845552706705</v>
+        <v>1.809046587995494</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05293532046885725</v>
+        <v>0.05199004688905623</v>
       </c>
       <c r="W57">
-        <v>0.2233178514334435</v>
+        <v>0.2235407469435606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1654228764651789</v>
+        <v>0.1624688965283007</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2064074019420047</v>
+        <v>0.2083074019420046</v>
       </c>
       <c r="C58">
-        <v>-28.7790055666285</v>
+        <v>-31.20576836280691</v>
       </c>
       <c r="D58">
-        <v>61.6469944333715</v>
+        <v>60.92623163719309</v>
       </c>
       <c r="E58">
-        <v>57.636</v>
+        <v>59.34200000000001</v>
       </c>
       <c r="F58">
-        <v>95.536</v>
+        <v>97.242</v>
       </c>
       <c r="G58">
         <v>5.11</v>
@@ -6043,37 +6043,37 @@
         <v>3.66</v>
       </c>
       <c r="M58">
-        <v>22.5273888</v>
+        <v>22.9296636</v>
       </c>
       <c r="N58">
-        <v>-18.8673888</v>
+        <v>-19.2696636</v>
       </c>
       <c r="O58">
-        <v>-6.037564416</v>
+        <v>-6.166292352</v>
       </c>
       <c r="P58">
-        <v>-12.829824384</v>
+        <v>-13.103371248</v>
       </c>
       <c r="Q58">
-        <v>-3.589824384</v>
+        <v>-3.863371248000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.184601326485479</v>
+        <v>0.1878292643107227</v>
       </c>
       <c r="T58">
-        <v>1.809046587995494</v>
+        <v>1.85111743887911</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05199004688905623</v>
+        <v>0.05107794080328331</v>
       </c>
       <c r="W58">
-        <v>0.2235407469435606</v>
+        <v>0.2237558215585858</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1624688965283007</v>
+        <v>0.1596185650102603</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2083074019420046</v>
+        <v>0.2102074019420047</v>
       </c>
       <c r="C59">
-        <v>-31.20576836280691</v>
+        <v>-33.61587194174128</v>
       </c>
       <c r="D59">
-        <v>60.92623163719309</v>
+        <v>60.22212805825873</v>
       </c>
       <c r="E59">
-        <v>59.34200000000001</v>
+        <v>61.04800000000001</v>
       </c>
       <c r="F59">
-        <v>97.242</v>
+        <v>98.94800000000001</v>
       </c>
       <c r="G59">
         <v>5.11</v>
@@ -6125,37 +6125,37 @@
         <v>3.66</v>
       </c>
       <c r="M59">
-        <v>22.9296636</v>
+        <v>23.3319384</v>
       </c>
       <c r="N59">
-        <v>-19.2696636</v>
+        <v>-19.6719384</v>
       </c>
       <c r="O59">
-        <v>-6.166292352</v>
+        <v>-6.295020288000001</v>
       </c>
       <c r="P59">
-        <v>-13.103371248</v>
+        <v>-13.376918112</v>
       </c>
       <c r="Q59">
-        <v>-3.863371248000002</v>
+        <v>-4.136918112000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1878292643107227</v>
+        <v>0.191210913460978</v>
       </c>
       <c r="T59">
-        <v>1.85111743887911</v>
+        <v>1.895191663614327</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05107794080328331</v>
+        <v>0.05019728665150255</v>
       </c>
       <c r="W59">
-        <v>0.2237558215585858</v>
+        <v>0.2239634798075757</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1596185650102603</v>
+        <v>0.1568665207859455</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2102074019420046</v>
+        <v>0.2121074019420047</v>
       </c>
       <c r="C60">
-        <v>-33.61587194174126</v>
+        <v>-36.00988727945061</v>
       </c>
       <c r="D60">
-        <v>60.22212805825873</v>
+        <v>59.53411272054938</v>
       </c>
       <c r="E60">
-        <v>61.04799999999999</v>
+        <v>62.754</v>
       </c>
       <c r="F60">
-        <v>98.94799999999999</v>
+        <v>100.654</v>
       </c>
       <c r="G60">
         <v>5.11</v>
@@ -6207,37 +6207,37 @@
         <v>3.66</v>
       </c>
       <c r="M60">
-        <v>23.3319384</v>
+        <v>23.7342132</v>
       </c>
       <c r="N60">
-        <v>-19.6719384</v>
+        <v>-20.0742132</v>
       </c>
       <c r="O60">
-        <v>-6.295020288</v>
+        <v>-6.423748224</v>
       </c>
       <c r="P60">
-        <v>-13.376918112</v>
+        <v>-13.650464976</v>
       </c>
       <c r="Q60">
-        <v>-4.136918111999998</v>
+        <v>-4.410464975999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1912109134609779</v>
+        <v>0.1947575211063677</v>
       </c>
       <c r="T60">
-        <v>1.895191663614327</v>
+        <v>1.941415850531749</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05019728665150257</v>
+        <v>0.04934648518283303</v>
       </c>
       <c r="W60">
-        <v>0.2239634798075757</v>
+        <v>0.224164098793888</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1568665207859455</v>
+        <v>0.1542077661963532</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2121074019420047</v>
+        <v>0.2140074019420047</v>
       </c>
       <c r="C61">
-        <v>-36.00988727945061</v>
+        <v>-38.38835955393498</v>
       </c>
       <c r="D61">
-        <v>59.53411272054938</v>
+        <v>58.86164044606502</v>
       </c>
       <c r="E61">
-        <v>62.754</v>
+        <v>64.46000000000001</v>
       </c>
       <c r="F61">
-        <v>100.654</v>
+        <v>102.36</v>
       </c>
       <c r="G61">
         <v>5.11</v>
@@ -6289,37 +6289,37 @@
         <v>3.66</v>
       </c>
       <c r="M61">
-        <v>23.7342132</v>
+        <v>24.136488</v>
       </c>
       <c r="N61">
-        <v>-20.0742132</v>
+        <v>-20.476488</v>
       </c>
       <c r="O61">
-        <v>-6.423748224</v>
+        <v>-6.55247616</v>
       </c>
       <c r="P61">
-        <v>-13.650464976</v>
+        <v>-13.92401184</v>
       </c>
       <c r="Q61">
-        <v>-4.410464975999998</v>
+        <v>-4.684011839999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1947575211063677</v>
+        <v>0.1984814591340268</v>
       </c>
       <c r="T61">
-        <v>1.941415850531749</v>
+        <v>1.989951246795043</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04934648518283303</v>
+        <v>0.04852404376311914</v>
       </c>
       <c r="W61">
-        <v>0.224164098793888</v>
+        <v>0.2243580304806565</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1542077661963532</v>
+        <v>0.1516376367597473</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2140074019420047</v>
+        <v>0.2159074019420046</v>
       </c>
       <c r="C62">
-        <v>-38.38835955393498</v>
+        <v>-40.75180958591918</v>
       </c>
       <c r="D62">
-        <v>58.86164044606502</v>
+        <v>58.20419041408081</v>
       </c>
       <c r="E62">
-        <v>64.46000000000001</v>
+        <v>66.166</v>
       </c>
       <c r="F62">
-        <v>102.36</v>
+        <v>104.066</v>
       </c>
       <c r="G62">
         <v>5.11</v>
@@ -6371,37 +6371,37 @@
         <v>3.66</v>
       </c>
       <c r="M62">
-        <v>24.136488</v>
+        <v>24.5387628</v>
       </c>
       <c r="N62">
-        <v>-20.476488</v>
+        <v>-20.8787628</v>
       </c>
       <c r="O62">
-        <v>-6.55247616</v>
+        <v>-6.681204095999999</v>
       </c>
       <c r="P62">
-        <v>-13.92401184</v>
+        <v>-14.197558704</v>
       </c>
       <c r="Q62">
-        <v>-4.684011839999998</v>
+        <v>-4.957558703999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1984814591340268</v>
+        <v>0.2023963683425916</v>
       </c>
       <c r="T62">
-        <v>1.989951246795043</v>
+        <v>2.040975637738506</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04852404376311914</v>
+        <v>0.0477285676358549</v>
       </c>
       <c r="W62">
-        <v>0.2243580304806565</v>
+        <v>0.2245456037514654</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1516376367597473</v>
+        <v>0.1491517738620466</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2159074019420046</v>
+        <v>0.2178074019420047</v>
       </c>
       <c r="C63">
-        <v>-40.75180958591918</v>
+        <v>-43.10073518410967</v>
       </c>
       <c r="D63">
-        <v>58.20419041408081</v>
+        <v>57.56126481589032</v>
       </c>
       <c r="E63">
-        <v>66.166</v>
+        <v>67.87199999999999</v>
       </c>
       <c r="F63">
-        <v>104.066</v>
+        <v>105.772</v>
       </c>
       <c r="G63">
         <v>5.11</v>
@@ -6453,37 +6453,37 @@
         <v>3.66</v>
       </c>
       <c r="M63">
-        <v>24.5387628</v>
+        <v>24.9410376</v>
       </c>
       <c r="N63">
-        <v>-20.8787628</v>
+        <v>-21.2810376</v>
       </c>
       <c r="O63">
-        <v>-6.681204095999999</v>
+        <v>-6.809932031999999</v>
       </c>
       <c r="P63">
-        <v>-14.197558704</v>
+        <v>-14.471105568</v>
       </c>
       <c r="Q63">
-        <v>-4.957558703999998</v>
+        <v>-5.231105567999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2023963683425916</v>
+        <v>0.2065173254042388</v>
       </c>
       <c r="T63">
-        <v>2.040975637738506</v>
+        <v>2.094685522942151</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0477285676358549</v>
+        <v>0.04695875202882498</v>
       </c>
       <c r="W63">
-        <v>0.2245456037514654</v>
+        <v>0.2247271262716031</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1491517738620466</v>
+        <v>0.146746100090078</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2178074019420047</v>
+        <v>0.2197074019420047</v>
       </c>
       <c r="C64">
-        <v>-43.10073518410967</v>
+        <v>-45.43561240226662</v>
       </c>
       <c r="D64">
-        <v>57.56126481589032</v>
+        <v>56.93238759773337</v>
       </c>
       <c r="E64">
-        <v>67.87199999999999</v>
+        <v>69.578</v>
       </c>
       <c r="F64">
-        <v>105.772</v>
+        <v>107.478</v>
       </c>
       <c r="G64">
         <v>5.11</v>
@@ -6535,37 +6535,37 @@
         <v>3.66</v>
       </c>
       <c r="M64">
-        <v>24.9410376</v>
+        <v>25.3433124</v>
       </c>
       <c r="N64">
-        <v>-21.2810376</v>
+        <v>-21.6833124</v>
       </c>
       <c r="O64">
-        <v>-6.809932031999999</v>
+        <v>-6.938659968</v>
       </c>
       <c r="P64">
-        <v>-14.471105568</v>
+        <v>-14.744652432</v>
       </c>
       <c r="Q64">
-        <v>-5.231105567999998</v>
+        <v>-5.504652431999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2065173254042388</v>
+        <v>0.2108610369016506</v>
       </c>
       <c r="T64">
-        <v>2.094685522942151</v>
+        <v>2.151298645183831</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04695875202882498</v>
+        <v>0.04621337501249442</v>
       </c>
       <c r="W64">
-        <v>0.2247271262716031</v>
+        <v>0.2249028861720538</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.146746100090078</v>
+        <v>0.1444167969140451</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2197074019420047</v>
+        <v>0.2216074019420047</v>
       </c>
       <c r="C65">
-        <v>-45.43561240226662</v>
+        <v>-47.75689671476319</v>
       </c>
       <c r="D65">
-        <v>56.93238759773337</v>
+        <v>56.31710328523681</v>
       </c>
       <c r="E65">
-        <v>69.578</v>
+        <v>71.28399999999999</v>
       </c>
       <c r="F65">
-        <v>107.478</v>
+        <v>109.184</v>
       </c>
       <c r="G65">
         <v>5.11</v>
@@ -6617,37 +6617,37 @@
         <v>3.66</v>
       </c>
       <c r="M65">
-        <v>25.3433124</v>
+        <v>25.7455872</v>
       </c>
       <c r="N65">
-        <v>-21.6833124</v>
+        <v>-22.0855872</v>
       </c>
       <c r="O65">
-        <v>-6.938659968</v>
+        <v>-7.067387904</v>
       </c>
       <c r="P65">
-        <v>-14.744652432</v>
+        <v>-15.018199296</v>
       </c>
       <c r="Q65">
-        <v>-5.504652431999999</v>
+        <v>-5.778199295999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2108610369016506</v>
+        <v>0.2154460657044743</v>
       </c>
       <c r="T65">
-        <v>2.151298645183831</v>
+        <v>2.211056940883382</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04621337501249442</v>
+        <v>0.0454912910279242</v>
       </c>
       <c r="W65">
-        <v>0.2249028861720538</v>
+        <v>0.2250731535756155</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1444167969140451</v>
+        <v>0.1421602844622631</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2216074019420047</v>
+        <v>0.2235074019420047</v>
       </c>
       <c r="C66">
-        <v>-47.75689671476319</v>
+        <v>-50.06502411673192</v>
       </c>
       <c r="D66">
-        <v>56.31710328523681</v>
+        <v>55.71497588326808</v>
       </c>
       <c r="E66">
-        <v>71.28399999999999</v>
+        <v>72.99000000000001</v>
       </c>
       <c r="F66">
-        <v>109.184</v>
+        <v>110.89</v>
       </c>
       <c r="G66">
         <v>5.11</v>
@@ -6699,37 +6699,37 @@
         <v>3.66</v>
       </c>
       <c r="M66">
-        <v>25.7455872</v>
+        <v>26.147862</v>
       </c>
       <c r="N66">
-        <v>-22.0855872</v>
+        <v>-22.487862</v>
       </c>
       <c r="O66">
-        <v>-7.067387904</v>
+        <v>-7.19611584</v>
       </c>
       <c r="P66">
-        <v>-15.018199296</v>
+        <v>-15.29174616</v>
       </c>
       <c r="Q66">
-        <v>-5.778199295999999</v>
+        <v>-6.051746159999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2154460657044743</v>
+        <v>0.2202930961531736</v>
       </c>
       <c r="T66">
-        <v>2.211056940883382</v>
+        <v>2.274229996337193</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0454912910279242</v>
+        <v>0.04479142501210998</v>
       </c>
       <c r="W66">
-        <v>0.2250731535756155</v>
+        <v>0.2252381819821445</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1421602844622631</v>
+        <v>0.1399732031628437</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2235074019420047</v>
+        <v>0.2254074019420046</v>
       </c>
       <c r="C67">
-        <v>-50.06502411673192</v>
+        <v>-52.36041215438301</v>
       </c>
       <c r="D67">
-        <v>55.71497588326808</v>
+        <v>55.12558784561699</v>
       </c>
       <c r="E67">
-        <v>72.99000000000001</v>
+        <v>74.696</v>
       </c>
       <c r="F67">
-        <v>110.89</v>
+        <v>112.596</v>
       </c>
       <c r="G67">
         <v>5.11</v>
@@ -6781,37 +6781,37 @@
         <v>3.66</v>
       </c>
       <c r="M67">
-        <v>26.147862</v>
+        <v>26.5501368</v>
       </c>
       <c r="N67">
-        <v>-22.487862</v>
+        <v>-22.8901368</v>
       </c>
       <c r="O67">
-        <v>-7.19611584</v>
+        <v>-7.324843776000001</v>
       </c>
       <c r="P67">
-        <v>-15.29174616</v>
+        <v>-15.565293024</v>
       </c>
       <c r="Q67">
-        <v>-6.051746159999999</v>
+        <v>-6.325293023999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2202930961531736</v>
+        <v>0.2254252460400316</v>
       </c>
       <c r="T67">
-        <v>2.274229996337193</v>
+        <v>2.341119113876522</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04479142501210998</v>
+        <v>0.04411276705738103</v>
       </c>
       <c r="W67">
-        <v>0.2252381819821445</v>
+        <v>0.2253982095278696</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1399732031628437</v>
+        <v>0.1378523970543157</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2254074019420046</v>
+        <v>0.2273074019420047</v>
       </c>
       <c r="C68">
-        <v>-52.36041215438301</v>
+        <v>-54.64346089061107</v>
       </c>
       <c r="D68">
-        <v>55.12558784561699</v>
+        <v>54.54853910938893</v>
       </c>
       <c r="E68">
-        <v>74.696</v>
+        <v>76.40200000000002</v>
       </c>
       <c r="F68">
-        <v>112.596</v>
+        <v>114.302</v>
       </c>
       <c r="G68">
         <v>5.11</v>
@@ -6863,37 +6863,37 @@
         <v>3.66</v>
       </c>
       <c r="M68">
-        <v>26.5501368</v>
+        <v>26.9524116</v>
       </c>
       <c r="N68">
-        <v>-22.8901368</v>
+        <v>-23.2924116</v>
       </c>
       <c r="O68">
-        <v>-7.324843776000001</v>
+        <v>-7.453571712</v>
       </c>
       <c r="P68">
-        <v>-15.565293024</v>
+        <v>-15.838839888</v>
       </c>
       <c r="Q68">
-        <v>-6.325293023999999</v>
+        <v>-6.598839888000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2254252460400316</v>
+        <v>0.2308684353139719</v>
       </c>
       <c r="T68">
-        <v>2.341119113876522</v>
+        <v>2.412062117327325</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04411276705738103</v>
+        <v>0.04345436754906192</v>
       </c>
       <c r="W68">
-        <v>0.2253982095278696</v>
+        <v>0.2255534601319312</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1378523970543157</v>
+        <v>0.1357948985908185</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2273074019420047</v>
+        <v>0.2292074019420047</v>
       </c>
       <c r="C69">
-        <v>-54.64346089061107</v>
+        <v>-56.91455381058283</v>
       </c>
       <c r="D69">
-        <v>54.54853910938893</v>
+        <v>53.98344618941718</v>
       </c>
       <c r="E69">
-        <v>76.40200000000002</v>
+        <v>78.108</v>
       </c>
       <c r="F69">
-        <v>114.302</v>
+        <v>116.008</v>
       </c>
       <c r="G69">
         <v>5.11</v>
@@ -6945,37 +6945,37 @@
         <v>3.66</v>
       </c>
       <c r="M69">
-        <v>26.9524116</v>
+        <v>27.3546864</v>
       </c>
       <c r="N69">
-        <v>-23.2924116</v>
+        <v>-23.6946864</v>
       </c>
       <c r="O69">
-        <v>-7.453571712</v>
+        <v>-7.582299648000001</v>
       </c>
       <c r="P69">
-        <v>-15.838839888</v>
+        <v>-16.112386752</v>
       </c>
       <c r="Q69">
-        <v>-6.598839888000001</v>
+        <v>-6.872386751999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2308684353139719</v>
+        <v>0.2366518239175336</v>
       </c>
       <c r="T69">
-        <v>2.412062117327325</v>
+        <v>2.487439058493805</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04345436754906192</v>
+        <v>0.04281533273216395</v>
       </c>
       <c r="W69">
-        <v>0.2255534601319312</v>
+        <v>0.2257041445417557</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1357948985908185</v>
+        <v>0.1337979147880123</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2292074019420047</v>
+        <v>0.2311074019420047</v>
       </c>
       <c r="C70">
-        <v>-56.91455381058283</v>
+        <v>-59.17405867161366</v>
       </c>
       <c r="D70">
-        <v>53.98344618941718</v>
+        <v>53.42994132838636</v>
       </c>
       <c r="E70">
-        <v>78.108</v>
+        <v>79.81400000000002</v>
       </c>
       <c r="F70">
-        <v>116.008</v>
+        <v>117.714</v>
       </c>
       <c r="G70">
         <v>5.11</v>
@@ -7027,37 +7027,37 @@
         <v>3.66</v>
       </c>
       <c r="M70">
-        <v>27.3546864</v>
+        <v>27.7569612</v>
       </c>
       <c r="N70">
-        <v>-23.6946864</v>
+        <v>-24.0969612</v>
       </c>
       <c r="O70">
-        <v>-7.582299648000001</v>
+        <v>-7.711027584000001</v>
       </c>
       <c r="P70">
-        <v>-16.112386752</v>
+        <v>-16.385933616</v>
       </c>
       <c r="Q70">
-        <v>-6.872386751999999</v>
+        <v>-7.145933616000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2366518239175336</v>
+        <v>0.2428083343664863</v>
       </c>
       <c r="T70">
-        <v>2.487439058493805</v>
+        <v>2.567679028122637</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04281533273216395</v>
+        <v>0.04219482066358186</v>
       </c>
       <c r="W70">
-        <v>0.2257041445417557</v>
+        <v>0.2258504612875274</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1337979147880123</v>
+        <v>0.1318588145736933</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2311074019420047</v>
+        <v>0.2330074019420046</v>
       </c>
       <c r="C71">
-        <v>-59.17405867161366</v>
+        <v>-61.42232830129091</v>
       </c>
       <c r="D71">
-        <v>53.42994132838636</v>
+        <v>52.88767169870909</v>
       </c>
       <c r="E71">
-        <v>79.81400000000002</v>
+        <v>81.52000000000001</v>
       </c>
       <c r="F71">
-        <v>117.714</v>
+        <v>119.42</v>
       </c>
       <c r="G71">
         <v>5.11</v>
@@ -7109,37 +7109,37 @@
         <v>3.66</v>
       </c>
       <c r="M71">
-        <v>27.7569612</v>
+        <v>28.159236</v>
       </c>
       <c r="N71">
-        <v>-24.0969612</v>
+        <v>-24.499236</v>
       </c>
       <c r="O71">
-        <v>-7.711027584000001</v>
+        <v>-7.83975552</v>
       </c>
       <c r="P71">
-        <v>-16.385933616</v>
+        <v>-16.65948048</v>
       </c>
       <c r="Q71">
-        <v>-7.145933616000002</v>
+        <v>-7.419480479999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2428083343664863</v>
+        <v>0.2493752788453692</v>
       </c>
       <c r="T71">
-        <v>2.567679028122637</v>
+        <v>2.653268329060058</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04219482066358186</v>
+        <v>0.04159203751124498</v>
       </c>
       <c r="W71">
-        <v>0.2258504612875274</v>
+        <v>0.2259925975548484</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1318588145736933</v>
+        <v>0.1299751172226405</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2330074019420046</v>
+        <v>0.2349074019420047</v>
       </c>
       <c r="C72">
-        <v>-61.42232830129091</v>
+        <v>-63.65970134748381</v>
       </c>
       <c r="D72">
-        <v>52.88767169870909</v>
+        <v>52.35629865251619</v>
       </c>
       <c r="E72">
-        <v>81.52000000000001</v>
+        <v>83.226</v>
       </c>
       <c r="F72">
-        <v>119.42</v>
+        <v>121.126</v>
       </c>
       <c r="G72">
         <v>5.11</v>
@@ -7191,37 +7191,37 @@
         <v>3.66</v>
       </c>
       <c r="M72">
-        <v>28.159236</v>
+        <v>28.5615108</v>
       </c>
       <c r="N72">
-        <v>-24.499236</v>
+        <v>-24.9015108</v>
       </c>
       <c r="O72">
-        <v>-7.83975552</v>
+        <v>-7.968483456</v>
       </c>
       <c r="P72">
-        <v>-16.65948048</v>
+        <v>-16.933027344</v>
       </c>
       <c r="Q72">
-        <v>-7.419480479999999</v>
+        <v>-7.693027343999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2493752788453692</v>
+        <v>0.2563951160469337</v>
       </c>
       <c r="T72">
-        <v>2.653268329060058</v>
+        <v>2.744760340406957</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04159203751124498</v>
+        <v>0.04100623416601618</v>
       </c>
       <c r="W72">
-        <v>0.2259925975548484</v>
+        <v>0.2261307299836534</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1299751172226405</v>
+        <v>0.1281444817688006</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2349074019420047</v>
+        <v>0.2368074019420046</v>
       </c>
       <c r="C73">
-        <v>-63.6597013474838</v>
+        <v>-65.88650298358993</v>
       </c>
       <c r="D73">
-        <v>52.35629865251619</v>
+        <v>51.83549701641005</v>
       </c>
       <c r="E73">
-        <v>83.226</v>
+        <v>84.93199999999999</v>
       </c>
       <c r="F73">
-        <v>121.126</v>
+        <v>122.832</v>
       </c>
       <c r="G73">
         <v>5.11</v>
@@ -7273,37 +7273,37 @@
         <v>3.66</v>
       </c>
       <c r="M73">
-        <v>28.5615108</v>
+        <v>28.9637856</v>
       </c>
       <c r="N73">
-        <v>-24.9015108</v>
+        <v>-25.3037856</v>
       </c>
       <c r="O73">
-        <v>-7.968483456</v>
+        <v>-8.097211392</v>
       </c>
       <c r="P73">
-        <v>-16.933027344</v>
+        <v>-17.206574208</v>
       </c>
       <c r="Q73">
-        <v>-7.693027343999999</v>
+        <v>-7.966574207999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2563951160469335</v>
+        <v>0.2639163701914669</v>
       </c>
       <c r="T73">
-        <v>2.744760340406956</v>
+        <v>2.84278749542149</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04100623416601618</v>
+        <v>0.04043670313593262</v>
       </c>
       <c r="W73">
-        <v>0.2261307299836534</v>
+        <v>0.2262650254005471</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1281444817688006</v>
+        <v>0.1263646972997894</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2368074019420046</v>
+        <v>0.2387074019420046</v>
       </c>
       <c r="C74">
-        <v>-65.88650298358993</v>
+        <v>-68.10304557210496</v>
       </c>
       <c r="D74">
-        <v>51.83549701641005</v>
+        <v>51.32495442789504</v>
       </c>
       <c r="E74">
-        <v>84.93199999999999</v>
+        <v>86.63800000000001</v>
       </c>
       <c r="F74">
-        <v>122.832</v>
+        <v>124.538</v>
       </c>
       <c r="G74">
         <v>5.11</v>
@@ -7355,37 +7355,37 @@
         <v>3.66</v>
       </c>
       <c r="M74">
-        <v>28.9637856</v>
+        <v>29.3660604</v>
       </c>
       <c r="N74">
-        <v>-25.3037856</v>
+        <v>-25.7060604</v>
       </c>
       <c r="O74">
-        <v>-8.097211392</v>
+        <v>-8.225939328000001</v>
       </c>
       <c r="P74">
-        <v>-17.206574208</v>
+        <v>-17.480121072</v>
       </c>
       <c r="Q74">
-        <v>-7.966574207999999</v>
+        <v>-8.240121072000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2639163701914669</v>
+        <v>0.2719947542726323</v>
       </c>
       <c r="T74">
-        <v>2.84278749542149</v>
+        <v>2.948075921177841</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04043670313593262</v>
+        <v>0.03988277569571436</v>
       </c>
       <c r="W74">
-        <v>0.2262650254005471</v>
+        <v>0.2263956414909505</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1263646972997894</v>
+        <v>0.1246336740491074</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2387074019420046</v>
+        <v>0.2406074019420046</v>
       </c>
       <c r="C75">
-        <v>-68.10304557210496</v>
+        <v>-70.30962928936039</v>
       </c>
       <c r="D75">
-        <v>51.32495442789504</v>
+        <v>50.82437071063961</v>
       </c>
       <c r="E75">
-        <v>86.63800000000001</v>
+        <v>88.34399999999999</v>
       </c>
       <c r="F75">
-        <v>124.538</v>
+        <v>126.244</v>
       </c>
       <c r="G75">
         <v>5.11</v>
@@ -7437,37 +7437,37 @@
         <v>3.66</v>
       </c>
       <c r="M75">
-        <v>29.3660604</v>
+        <v>29.7683352</v>
       </c>
       <c r="N75">
-        <v>-25.7060604</v>
+        <v>-26.1083352</v>
       </c>
       <c r="O75">
-        <v>-8.225939328000001</v>
+        <v>-8.354667264000001</v>
       </c>
       <c r="P75">
-        <v>-17.480121072</v>
+        <v>-17.753667936</v>
       </c>
       <c r="Q75">
-        <v>-8.240121072000003</v>
+        <v>-8.513667935999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2719947542726323</v>
+        <v>0.2806945525138874</v>
       </c>
       <c r="T75">
-        <v>2.948075921177841</v>
+        <v>3.061463456607759</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03988277569571436</v>
+        <v>0.0393438192673939</v>
       </c>
       <c r="W75">
-        <v>0.2263956414909505</v>
+        <v>0.2265227274167485</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1246336740491074</v>
+        <v>0.122949435210606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2406074019420046</v>
+        <v>0.2425074019420047</v>
       </c>
       <c r="C76">
-        <v>-70.30962928936039</v>
+        <v>-72.50654271405544</v>
       </c>
       <c r="D76">
-        <v>50.82437071063961</v>
+        <v>50.33345728594455</v>
       </c>
       <c r="E76">
-        <v>88.34399999999999</v>
+        <v>90.04999999999998</v>
       </c>
       <c r="F76">
-        <v>126.244</v>
+        <v>127.95</v>
       </c>
       <c r="G76">
         <v>5.11</v>
@@ -7519,37 +7519,37 @@
         <v>3.66</v>
       </c>
       <c r="M76">
-        <v>29.7683352</v>
+        <v>30.17061</v>
       </c>
       <c r="N76">
-        <v>-26.1083352</v>
+        <v>-26.51061</v>
       </c>
       <c r="O76">
-        <v>-8.354667264000001</v>
+        <v>-8.4833952</v>
       </c>
       <c r="P76">
-        <v>-17.753667936</v>
+        <v>-18.0272148</v>
       </c>
       <c r="Q76">
-        <v>-8.513667935999999</v>
+        <v>-8.787214799999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2806945525138874</v>
+        <v>0.2900903346144429</v>
       </c>
       <c r="T76">
-        <v>3.061463456607759</v>
+        <v>3.183921994872069</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0393438192673939</v>
+        <v>0.03881923501049532</v>
       </c>
       <c r="W76">
-        <v>0.2265227274167485</v>
+        <v>0.2266464243845252</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.122949435210606</v>
+        <v>0.1213101094077979</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2425074019420047</v>
+        <v>0.2444074019420047</v>
       </c>
       <c r="C77">
-        <v>-72.50654271405544</v>
+        <v>-74.6940633820073</v>
       </c>
       <c r="D77">
-        <v>50.33345728594455</v>
+        <v>49.8519366179927</v>
       </c>
       <c r="E77">
-        <v>90.04999999999998</v>
+        <v>91.756</v>
       </c>
       <c r="F77">
-        <v>127.95</v>
+        <v>129.656</v>
       </c>
       <c r="G77">
         <v>5.11</v>
@@ -7601,37 +7601,37 @@
         <v>3.66</v>
       </c>
       <c r="M77">
-        <v>30.17061</v>
+        <v>30.5728848</v>
       </c>
       <c r="N77">
-        <v>-26.51061</v>
+        <v>-26.9128848</v>
       </c>
       <c r="O77">
-        <v>-8.4833952</v>
+        <v>-8.612123136000001</v>
       </c>
       <c r="P77">
-        <v>-18.0272148</v>
+        <v>-18.300761664</v>
       </c>
       <c r="Q77">
-        <v>-8.787214799999999</v>
+        <v>-9.060761664000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2900903346144429</v>
+        <v>0.3002690985567115</v>
       </c>
       <c r="T77">
-        <v>3.183921994872069</v>
+        <v>3.316585411325073</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03881923501049532</v>
+        <v>0.03830845560246248</v>
       </c>
       <c r="W77">
-        <v>0.2266464243845252</v>
+        <v>0.2267668661689394</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1213101094077979</v>
+        <v>0.1197139237576952</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2444074019420047</v>
+        <v>0.2463074019420046</v>
       </c>
       <c r="C78">
-        <v>-74.6940633820073</v>
+        <v>-76.87245830936055</v>
       </c>
       <c r="D78">
-        <v>49.8519366179927</v>
+        <v>49.37954169063945</v>
       </c>
       <c r="E78">
-        <v>91.756</v>
+        <v>93.46199999999999</v>
       </c>
       <c r="F78">
-        <v>129.656</v>
+        <v>131.362</v>
       </c>
       <c r="G78">
         <v>5.11</v>
@@ -7683,37 +7683,37 @@
         <v>3.66</v>
       </c>
       <c r="M78">
-        <v>30.5728848</v>
+        <v>30.9751596</v>
       </c>
       <c r="N78">
-        <v>-26.9128848</v>
+        <v>-27.3151596</v>
       </c>
       <c r="O78">
-        <v>-8.612123136000001</v>
+        <v>-8.740851072</v>
       </c>
       <c r="P78">
-        <v>-18.300761664</v>
+        <v>-18.574308528</v>
       </c>
       <c r="Q78">
-        <v>-9.060761664000003</v>
+        <v>-9.334308528000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3002690985567115</v>
+        <v>0.3113329724070032</v>
       </c>
       <c r="T78">
-        <v>3.316585411325073</v>
+        <v>3.460784777034858</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03830845560246248</v>
+        <v>0.03781094319204089</v>
       </c>
       <c r="W78">
-        <v>0.2267668661689394</v>
+        <v>0.2268841795953168</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1197139237576952</v>
+        <v>0.1181591974751278</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2463074019420046</v>
+        <v>0.2482074019420047</v>
       </c>
       <c r="C79">
-        <v>-76.87245830936055</v>
+        <v>-79.04198448632863</v>
       </c>
       <c r="D79">
-        <v>49.37954169063945</v>
+        <v>48.91601551367138</v>
       </c>
       <c r="E79">
-        <v>93.46199999999999</v>
+        <v>95.16800000000001</v>
       </c>
       <c r="F79">
-        <v>131.362</v>
+        <v>133.068</v>
       </c>
       <c r="G79">
         <v>5.11</v>
@@ -7765,37 +7765,37 @@
         <v>3.66</v>
       </c>
       <c r="M79">
-        <v>30.9751596</v>
+        <v>31.37743440000001</v>
       </c>
       <c r="N79">
-        <v>-27.3151596</v>
+        <v>-27.71743440000001</v>
       </c>
       <c r="O79">
-        <v>-8.740851072</v>
+        <v>-8.869579008000002</v>
       </c>
       <c r="P79">
-        <v>-18.574308528</v>
+        <v>-18.847855392</v>
       </c>
       <c r="Q79">
-        <v>-9.334308528000003</v>
+        <v>-9.607855392000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3113329724070032</v>
+        <v>0.3234026529709579</v>
       </c>
       <c r="T79">
-        <v>3.460784777034858</v>
+        <v>3.618093175990988</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03781094319204089</v>
+        <v>0.03732618751009164</v>
       </c>
       <c r="W79">
-        <v>0.2268841795953168</v>
+        <v>0.2269984849851204</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1181591974751278</v>
+        <v>0.1166443359690363</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2482074019420047</v>
+        <v>0.2501074019420046</v>
       </c>
       <c r="C80">
-        <v>-79.04198448632863</v>
+        <v>-81.20288934338492</v>
       </c>
       <c r="D80">
-        <v>48.91601551367138</v>
+        <v>48.46111065661507</v>
       </c>
       <c r="E80">
-        <v>95.16800000000001</v>
+        <v>96.874</v>
       </c>
       <c r="F80">
-        <v>133.068</v>
+        <v>134.774</v>
       </c>
       <c r="G80">
         <v>5.11</v>
@@ -7847,37 +7847,37 @@
         <v>3.66</v>
       </c>
       <c r="M80">
-        <v>31.37743440000001</v>
+        <v>31.7797092</v>
       </c>
       <c r="N80">
-        <v>-27.71743440000001</v>
+        <v>-28.1197092</v>
       </c>
       <c r="O80">
-        <v>-8.869579008000002</v>
+        <v>-8.998306944000001</v>
       </c>
       <c r="P80">
-        <v>-18.847855392</v>
+        <v>-19.121402256</v>
       </c>
       <c r="Q80">
-        <v>-9.607855392000003</v>
+        <v>-9.881402256000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3234026529709579</v>
+        <v>0.336621826921956</v>
       </c>
       <c r="T80">
-        <v>3.618093175990988</v>
+        <v>3.790383327228655</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03732618751009164</v>
+        <v>0.03685370412388796</v>
       </c>
       <c r="W80">
-        <v>0.2269984849851204</v>
+        <v>0.2271098965675872</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1166443359690363</v>
+        <v>0.1151678253871499</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2501074019420046</v>
+        <v>0.2520074019420047</v>
       </c>
       <c r="C81">
-        <v>-81.20288934338492</v>
+        <v>-83.35541119168147</v>
       </c>
       <c r="D81">
-        <v>48.46111065661507</v>
+        <v>48.01458880831852</v>
       </c>
       <c r="E81">
-        <v>96.874</v>
+        <v>98.57999999999998</v>
       </c>
       <c r="F81">
-        <v>134.774</v>
+        <v>136.48</v>
       </c>
       <c r="G81">
         <v>5.11</v>
@@ -7929,37 +7929,37 @@
         <v>3.66</v>
       </c>
       <c r="M81">
-        <v>31.7797092</v>
+        <v>32.181984</v>
       </c>
       <c r="N81">
-        <v>-28.1197092</v>
+        <v>-28.521984</v>
       </c>
       <c r="O81">
-        <v>-8.998306944000001</v>
+        <v>-9.12703488</v>
       </c>
       <c r="P81">
-        <v>-19.121402256</v>
+        <v>-19.39494912</v>
       </c>
       <c r="Q81">
-        <v>-9.881402256000003</v>
+        <v>-10.15494912</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.336621826921956</v>
+        <v>0.3511629182680537</v>
       </c>
       <c r="T81">
-        <v>3.790383327228655</v>
+        <v>3.979902493590087</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03685370412388796</v>
+        <v>0.03639303282233936</v>
       </c>
       <c r="W81">
-        <v>0.2271098965675872</v>
+        <v>0.2272185228604924</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1151678253871499</v>
+        <v>0.1137282275698105</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2520074019420047</v>
+        <v>0.2539074019420047</v>
       </c>
       <c r="C82">
-        <v>-83.35541119168147</v>
+        <v>-85.49977963934116</v>
       </c>
       <c r="D82">
-        <v>48.01458880831852</v>
+        <v>47.57622036065885</v>
       </c>
       <c r="E82">
-        <v>98.57999999999998</v>
+        <v>100.286</v>
       </c>
       <c r="F82">
-        <v>136.48</v>
+        <v>138.186</v>
       </c>
       <c r="G82">
         <v>5.11</v>
@@ -8011,37 +8011,37 @@
         <v>3.66</v>
       </c>
       <c r="M82">
-        <v>32.181984</v>
+        <v>32.5842588</v>
       </c>
       <c r="N82">
-        <v>-28.521984</v>
+        <v>-28.9242588</v>
       </c>
       <c r="O82">
-        <v>-9.12703488</v>
+        <v>-9.255762816000001</v>
       </c>
       <c r="P82">
-        <v>-19.39494912</v>
+        <v>-19.668495984</v>
       </c>
       <c r="Q82">
-        <v>-10.15494912</v>
+        <v>-10.428495984</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3511629182680537</v>
+        <v>0.3672346508084777</v>
       </c>
       <c r="T82">
-        <v>3.979902493590087</v>
+        <v>4.189371045884303</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03639303282233936</v>
+        <v>0.035943736120829</v>
       </c>
       <c r="W82">
-        <v>0.2272185228604924</v>
+        <v>0.2273244670227085</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1137282275698105</v>
+        <v>0.1123241753775907</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2539074019420047</v>
+        <v>0.2558074019420047</v>
       </c>
       <c r="C83">
-        <v>-85.49977963934116</v>
+        <v>-87.63621598515249</v>
       </c>
       <c r="D83">
-        <v>47.57622036065885</v>
+        <v>47.14578401484751</v>
       </c>
       <c r="E83">
-        <v>100.286</v>
+        <v>101.992</v>
       </c>
       <c r="F83">
-        <v>138.186</v>
+        <v>139.892</v>
       </c>
       <c r="G83">
         <v>5.11</v>
@@ -8093,37 +8093,37 @@
         <v>3.66</v>
       </c>
       <c r="M83">
-        <v>32.5842588</v>
+        <v>32.9865336</v>
       </c>
       <c r="N83">
-        <v>-28.9242588</v>
+        <v>-29.3265336</v>
       </c>
       <c r="O83">
-        <v>-9.255762816000001</v>
+        <v>-9.384490752000001</v>
       </c>
       <c r="P83">
-        <v>-19.668495984</v>
+        <v>-19.942042848</v>
       </c>
       <c r="Q83">
-        <v>-10.428495984</v>
+        <v>-10.702042848</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3672346508084777</v>
+        <v>0.3850921314089487</v>
       </c>
       <c r="T83">
-        <v>4.189371045884303</v>
+        <v>4.422113881766764</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.035943736120829</v>
+        <v>0.03550539787545303</v>
       </c>
       <c r="W83">
-        <v>0.2273244670227085</v>
+        <v>0.2274278271809682</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1123241753775907</v>
+        <v>0.1109543683607908</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2558074019420047</v>
+        <v>0.2577074019420046</v>
       </c>
       <c r="C84">
-        <v>-87.63621598515249</v>
+        <v>-89.76493359108457</v>
       </c>
       <c r="D84">
-        <v>47.14578401484751</v>
+        <v>46.72306640891544</v>
       </c>
       <c r="E84">
-        <v>101.992</v>
+        <v>103.698</v>
       </c>
       <c r="F84">
-        <v>139.892</v>
+        <v>141.598</v>
       </c>
       <c r="G84">
         <v>5.11</v>
@@ -8175,37 +8175,37 @@
         <v>3.66</v>
       </c>
       <c r="M84">
-        <v>32.9865336</v>
+        <v>33.3888084</v>
       </c>
       <c r="N84">
-        <v>-29.3265336</v>
+        <v>-29.7288084</v>
       </c>
       <c r="O84">
-        <v>-9.384490752000001</v>
+        <v>-9.513218688</v>
       </c>
       <c r="P84">
-        <v>-19.942042848</v>
+        <v>-20.215589712</v>
       </c>
       <c r="Q84">
-        <v>-10.702042848</v>
+        <v>-10.975589712</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3850921314089487</v>
+        <v>0.4050504920800633</v>
       </c>
       <c r="T84">
-        <v>4.422113881766764</v>
+        <v>4.682238227753045</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03550539787545303</v>
+        <v>0.03507762199743553</v>
       </c>
       <c r="W84">
-        <v>0.2274278271809682</v>
+        <v>0.2275286967330047</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1109543683607908</v>
+        <v>0.109617568741986</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2577074019420046</v>
+        <v>0.2596074019420047</v>
       </c>
       <c r="C85">
-        <v>-89.76493359108457</v>
+        <v>-91.88613823493979</v>
       </c>
       <c r="D85">
-        <v>46.72306640891544</v>
+        <v>46.30786176506021</v>
       </c>
       <c r="E85">
-        <v>103.698</v>
+        <v>105.404</v>
       </c>
       <c r="F85">
-        <v>141.598</v>
+        <v>143.304</v>
       </c>
       <c r="G85">
         <v>5.11</v>
@@ -8257,37 +8257,37 @@
         <v>3.66</v>
       </c>
       <c r="M85">
-        <v>33.3888084</v>
+        <v>33.7910832</v>
       </c>
       <c r="N85">
-        <v>-29.7288084</v>
+        <v>-30.1310832</v>
       </c>
       <c r="O85">
-        <v>-9.513218688</v>
+        <v>-9.641946624000001</v>
       </c>
       <c r="P85">
-        <v>-20.215589712</v>
+        <v>-20.489136576</v>
       </c>
       <c r="Q85">
-        <v>-10.975589712</v>
+        <v>-11.249136576</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4050504920800633</v>
+        <v>0.4275036478350673</v>
       </c>
       <c r="T85">
-        <v>4.682238227753045</v>
+        <v>4.974878116987611</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03507762199743553</v>
+        <v>0.03466003125937082</v>
       </c>
       <c r="W85">
-        <v>0.2275286967330047</v>
+        <v>0.2276271646290404</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.109617568741986</v>
+        <v>0.1083125976855338</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2596074019420046</v>
+        <v>0.2615074019420046</v>
       </c>
       <c r="C86">
-        <v>-91.88613823493978</v>
+        <v>-94.00002844436925</v>
       </c>
       <c r="D86">
-        <v>46.30786176506023</v>
+        <v>45.89997155563074</v>
       </c>
       <c r="E86">
-        <v>105.404</v>
+        <v>107.11</v>
       </c>
       <c r="F86">
-        <v>143.304</v>
+        <v>145.01</v>
       </c>
       <c r="G86">
         <v>5.11</v>
@@ -8339,37 +8339,37 @@
         <v>3.66</v>
       </c>
       <c r="M86">
-        <v>33.7910832</v>
+        <v>34.193358</v>
       </c>
       <c r="N86">
-        <v>-30.1310832</v>
+        <v>-30.533358</v>
       </c>
       <c r="O86">
-        <v>-9.641946624000001</v>
+        <v>-9.77067456</v>
       </c>
       <c r="P86">
-        <v>-20.489136576</v>
+        <v>-20.76268344</v>
       </c>
       <c r="Q86">
-        <v>-11.249136576</v>
+        <v>-11.52268344</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4275036478350671</v>
+        <v>0.4529505576907382</v>
       </c>
       <c r="T86">
-        <v>4.974878116987608</v>
+        <v>5.306536658120115</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03466003125937082</v>
+        <v>0.03425226618573116</v>
       </c>
       <c r="W86">
-        <v>0.2276271646290404</v>
+        <v>0.2277233156334046</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1083125976855338</v>
+        <v>0.1070383318304099</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2615074019420046</v>
+        <v>0.2634074019420047</v>
       </c>
       <c r="C87">
-        <v>-94.00002844436925</v>
+        <v>-96.10679581338982</v>
       </c>
       <c r="D87">
-        <v>45.89997155563074</v>
+        <v>45.49920418661015</v>
       </c>
       <c r="E87">
-        <v>107.11</v>
+        <v>108.816</v>
       </c>
       <c r="F87">
-        <v>145.01</v>
+        <v>146.716</v>
       </c>
       <c r="G87">
         <v>5.11</v>
@@ -8421,37 +8421,37 @@
         <v>3.66</v>
       </c>
       <c r="M87">
-        <v>34.193358</v>
+        <v>34.5956328</v>
       </c>
       <c r="N87">
-        <v>-30.533358</v>
+        <v>-30.9356328</v>
       </c>
       <c r="O87">
-        <v>-9.77067456</v>
+        <v>-9.899402495999999</v>
       </c>
       <c r="P87">
-        <v>-20.76268344</v>
+        <v>-21.036230304</v>
       </c>
       <c r="Q87">
-        <v>-11.52268344</v>
+        <v>-11.796230304</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4529505576907382</v>
+        <v>0.4820327403829339</v>
       </c>
       <c r="T87">
-        <v>5.306536658120115</v>
+        <v>5.685574990842981</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03425226618573116</v>
+        <v>0.0338539840207808</v>
       </c>
       <c r="W87">
-        <v>0.2277233156334046</v>
+        <v>0.2278172305678999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1070383318304099</v>
+        <v>0.10579370006494</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2634074019420047</v>
+        <v>0.2653074019420046</v>
       </c>
       <c r="C88">
-        <v>-96.10679581338982</v>
+        <v>-98.20662530246283</v>
       </c>
       <c r="D88">
-        <v>45.49920418661015</v>
+        <v>45.10537469753717</v>
       </c>
       <c r="E88">
-        <v>108.816</v>
+        <v>110.522</v>
       </c>
       <c r="F88">
-        <v>146.716</v>
+        <v>148.422</v>
       </c>
       <c r="G88">
         <v>5.11</v>
@@ -8503,37 +8503,37 @@
         <v>3.66</v>
       </c>
       <c r="M88">
-        <v>34.5956328</v>
+        <v>34.9979076</v>
       </c>
       <c r="N88">
-        <v>-30.9356328</v>
+        <v>-31.3379076</v>
       </c>
       <c r="O88">
-        <v>-9.899402495999999</v>
+        <v>-10.028130432</v>
       </c>
       <c r="P88">
-        <v>-21.036230304</v>
+        <v>-21.309777168</v>
       </c>
       <c r="Q88">
-        <v>-11.796230304</v>
+        <v>-12.069777168</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4820327403829339</v>
+        <v>0.5155891050277748</v>
       </c>
       <c r="T88">
-        <v>5.685574990842981</v>
+        <v>6.122926913215517</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0338539840207808</v>
+        <v>0.03346485776766838</v>
       </c>
       <c r="W88">
-        <v>0.2278172305678999</v>
+        <v>0.2279089865383838</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.10579370006494</v>
+        <v>0.1045776805239637</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2653074019420046</v>
+        <v>0.2672074019420047</v>
       </c>
       <c r="C89">
-        <v>-98.20662530246283</v>
+        <v>-100.2996955231222</v>
       </c>
       <c r="D89">
-        <v>45.10537469753717</v>
+        <v>44.71830447687775</v>
       </c>
       <c r="E89">
-        <v>110.522</v>
+        <v>112.228</v>
       </c>
       <c r="F89">
-        <v>148.422</v>
+        <v>150.128</v>
       </c>
       <c r="G89">
         <v>5.11</v>
@@ -8585,37 +8585,37 @@
         <v>3.66</v>
       </c>
       <c r="M89">
-        <v>34.9979076</v>
+        <v>35.4001824</v>
       </c>
       <c r="N89">
-        <v>-31.3379076</v>
+        <v>-31.7401824</v>
       </c>
       <c r="O89">
-        <v>-10.028130432</v>
+        <v>-10.156858368</v>
       </c>
       <c r="P89">
-        <v>-21.309777168</v>
+        <v>-21.583324032</v>
       </c>
       <c r="Q89">
-        <v>-12.069777168</v>
+        <v>-12.343324032</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5155891050277748</v>
+        <v>0.5547381971134229</v>
       </c>
       <c r="T89">
-        <v>6.122926913215517</v>
+        <v>6.633170822650145</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03346485776766838</v>
+        <v>0.03308457529303578</v>
       </c>
       <c r="W89">
-        <v>0.2279089865383838</v>
+        <v>0.2279986571459022</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1045776805239637</v>
+        <v>0.1033892977907368</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2672074019420047</v>
+        <v>0.2691074019420046</v>
       </c>
       <c r="C90">
-        <v>-100.2996955231222</v>
+        <v>-102.3861790080724</v>
       </c>
       <c r="D90">
-        <v>44.71830447687775</v>
+        <v>44.33782099192757</v>
       </c>
       <c r="E90">
-        <v>112.228</v>
+        <v>113.934</v>
       </c>
       <c r="F90">
-        <v>150.128</v>
+        <v>151.834</v>
       </c>
       <c r="G90">
         <v>5.11</v>
@@ -8667,37 +8667,37 @@
         <v>3.66</v>
       </c>
       <c r="M90">
-        <v>35.4001824</v>
+        <v>35.8024572</v>
       </c>
       <c r="N90">
-        <v>-31.7401824</v>
+        <v>-32.1424572</v>
       </c>
       <c r="O90">
-        <v>-10.156858368</v>
+        <v>-10.285586304</v>
       </c>
       <c r="P90">
-        <v>-21.583324032</v>
+        <v>-21.856870896</v>
       </c>
       <c r="Q90">
-        <v>-12.343324032</v>
+        <v>-12.616870896</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5547381971134229</v>
+        <v>0.6010053059419158</v>
       </c>
       <c r="T90">
-        <v>6.633170822650145</v>
+        <v>7.236186351981976</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03308457529303578</v>
+        <v>0.03271283849199044</v>
       </c>
       <c r="W90">
-        <v>0.2279986571459022</v>
+        <v>0.2280863126835886</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1033892977907368</v>
+        <v>0.1022276202874702</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2691074019420046</v>
+        <v>0.2710074019420046</v>
       </c>
       <c r="C91">
-        <v>-102.3861790080724</v>
+        <v>-104.4662424676134</v>
       </c>
       <c r="D91">
-        <v>44.33782099192757</v>
+        <v>43.96375753238657</v>
       </c>
       <c r="E91">
-        <v>113.934</v>
+        <v>115.64</v>
       </c>
       <c r="F91">
-        <v>151.834</v>
+        <v>153.54</v>
       </c>
       <c r="G91">
         <v>5.11</v>
@@ -8749,37 +8749,37 @@
         <v>3.66</v>
       </c>
       <c r="M91">
-        <v>35.8024572</v>
+        <v>36.204732</v>
       </c>
       <c r="N91">
-        <v>-32.1424572</v>
+        <v>-32.544732</v>
       </c>
       <c r="O91">
-        <v>-10.285586304</v>
+        <v>-10.41431424</v>
       </c>
       <c r="P91">
-        <v>-21.856870896</v>
+        <v>-22.13041776</v>
       </c>
       <c r="Q91">
-        <v>-12.616870896</v>
+        <v>-12.89041776</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6010053059419158</v>
+        <v>0.6565258365361074</v>
       </c>
       <c r="T91">
-        <v>7.236186351981976</v>
+        <v>7.959804987180174</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03271283849199044</v>
+        <v>0.03234936250874609</v>
       </c>
       <c r="W91">
-        <v>0.2280863126835886</v>
+        <v>0.2281720203204377</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1022276202874702</v>
+        <v>0.1010917578398316</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2710074019420046</v>
+        <v>0.2729074019420046</v>
       </c>
       <c r="C92">
-        <v>-104.4662424676134</v>
+        <v>-106.5400470331945</v>
       </c>
       <c r="D92">
-        <v>43.96375753238657</v>
+        <v>43.59595296680547</v>
       </c>
       <c r="E92">
-        <v>115.64</v>
+        <v>117.346</v>
       </c>
       <c r="F92">
-        <v>153.54</v>
+        <v>155.246</v>
       </c>
       <c r="G92">
         <v>5.11</v>
@@ -8831,37 +8831,37 @@
         <v>3.66</v>
       </c>
       <c r="M92">
-        <v>36.204732</v>
+        <v>36.6070068</v>
       </c>
       <c r="N92">
-        <v>-32.544732</v>
+        <v>-32.9470068</v>
       </c>
       <c r="O92">
-        <v>-10.41431424</v>
+        <v>-10.543042176</v>
       </c>
       <c r="P92">
-        <v>-22.13041776</v>
+        <v>-22.403964624</v>
       </c>
       <c r="Q92">
-        <v>-12.89041776</v>
+        <v>-13.163964624</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6565258365361074</v>
+        <v>0.7243842628178973</v>
       </c>
       <c r="T92">
-        <v>7.959804987180174</v>
+        <v>8.844227763533528</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03234936250874609</v>
+        <v>0.03199387500864999</v>
       </c>
       <c r="W92">
-        <v>0.2281720203204377</v>
+        <v>0.2282558442729603</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1010917578398316</v>
+        <v>0.09998085940203127</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2729074019420046</v>
+        <v>0.2748074019420047</v>
       </c>
       <c r="C93">
-        <v>-106.5400470331945</v>
+        <v>-108.607748488844</v>
       </c>
       <c r="D93">
-        <v>43.59595296680547</v>
+        <v>43.23425151115596</v>
       </c>
       <c r="E93">
-        <v>117.346</v>
+        <v>119.052</v>
       </c>
       <c r="F93">
-        <v>155.246</v>
+        <v>156.952</v>
       </c>
       <c r="G93">
         <v>5.11</v>
@@ -8913,37 +8913,37 @@
         <v>3.66</v>
       </c>
       <c r="M93">
-        <v>36.6070068</v>
+        <v>37.0092816</v>
       </c>
       <c r="N93">
-        <v>-32.9470068</v>
+        <v>-33.3492816</v>
       </c>
       <c r="O93">
-        <v>-10.543042176</v>
+        <v>-10.671770112</v>
       </c>
       <c r="P93">
-        <v>-22.403964624</v>
+        <v>-22.677511488</v>
       </c>
       <c r="Q93">
-        <v>-13.163964624</v>
+        <v>-13.437511488</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7243842628178973</v>
+        <v>0.8092072956701346</v>
       </c>
       <c r="T93">
-        <v>8.844227763533528</v>
+        <v>9.949756233975222</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03199387500864999</v>
+        <v>0.0316461154976864</v>
       </c>
       <c r="W93">
-        <v>0.2282558442729603</v>
+        <v>0.2283378459656456</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09998085940203127</v>
+        <v>0.09889411093027012</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2748074019420047</v>
+        <v>0.2767074019420047</v>
       </c>
       <c r="C94">
-        <v>-108.607748488844</v>
+        <v>-110.6694974911728</v>
       </c>
       <c r="D94">
-        <v>43.23425151115596</v>
+        <v>42.8785025088272</v>
       </c>
       <c r="E94">
-        <v>119.052</v>
+        <v>120.758</v>
       </c>
       <c r="F94">
-        <v>156.952</v>
+        <v>158.658</v>
       </c>
       <c r="G94">
         <v>5.11</v>
@@ -8995,37 +8995,37 @@
         <v>3.66</v>
       </c>
       <c r="M94">
-        <v>37.0092816</v>
+        <v>37.4115564</v>
       </c>
       <c r="N94">
-        <v>-33.3492816</v>
+        <v>-33.7515564</v>
       </c>
       <c r="O94">
-        <v>-10.671770112</v>
+        <v>-10.800498048</v>
       </c>
       <c r="P94">
-        <v>-22.677511488</v>
+        <v>-22.951058352</v>
       </c>
       <c r="Q94">
-        <v>-13.437511488</v>
+        <v>-13.711058352</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8092072956701346</v>
+        <v>0.9182654807658683</v>
       </c>
       <c r="T94">
-        <v>9.949756233975222</v>
+        <v>11.37114998168597</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0316461154976864</v>
+        <v>0.03130583468588332</v>
       </c>
       <c r="W94">
-        <v>0.2283378459656456</v>
+        <v>0.2284180841810687</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.09889411093027012</v>
+        <v>0.09783073339338544</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2767074019420047</v>
+        <v>0.2786074019420047</v>
       </c>
       <c r="C95">
-        <v>-110.6694974911728</v>
+        <v>-112.7254397786052</v>
       </c>
       <c r="D95">
-        <v>42.8785025088272</v>
+        <v>42.52856022139483</v>
       </c>
       <c r="E95">
-        <v>120.758</v>
+        <v>122.464</v>
       </c>
       <c r="F95">
-        <v>158.658</v>
+        <v>160.364</v>
       </c>
       <c r="G95">
         <v>5.11</v>
@@ -9077,37 +9077,37 @@
         <v>3.66</v>
       </c>
       <c r="M95">
-        <v>37.4115564</v>
+        <v>37.8138312</v>
       </c>
       <c r="N95">
-        <v>-33.7515564</v>
+        <v>-34.1538312</v>
       </c>
       <c r="O95">
-        <v>-10.800498048</v>
+        <v>-10.929225984</v>
       </c>
       <c r="P95">
-        <v>-22.951058352</v>
+        <v>-23.224605216</v>
       </c>
       <c r="Q95">
-        <v>-13.711058352</v>
+        <v>-13.984605216</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9182654807658683</v>
+        <v>1.063676394226847</v>
       </c>
       <c r="T95">
-        <v>11.37114998168597</v>
+        <v>13.2663416453003</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03130583468588332</v>
+        <v>0.03097279389135264</v>
       </c>
       <c r="W95">
-        <v>0.2284180841810687</v>
+        <v>0.2284966152004191</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.09783073339338544</v>
+        <v>0.09678998091047708</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2786074019420047</v>
+        <v>0.2805074019420046</v>
       </c>
       <c r="C96">
-        <v>-112.7254397786052</v>
+        <v>-114.775716370447</v>
       </c>
       <c r="D96">
-        <v>42.52856022139483</v>
+        <v>42.18428362955299</v>
       </c>
       <c r="E96">
-        <v>122.464</v>
+        <v>124.17</v>
       </c>
       <c r="F96">
-        <v>160.364</v>
+        <v>162.07</v>
       </c>
       <c r="G96">
         <v>5.11</v>
@@ -9159,37 +9159,37 @@
         <v>3.66</v>
       </c>
       <c r="M96">
-        <v>37.8138312</v>
+        <v>38.216106</v>
       </c>
       <c r="N96">
-        <v>-34.1538312</v>
+        <v>-34.556106</v>
       </c>
       <c r="O96">
-        <v>-10.929225984</v>
+        <v>-11.05795392</v>
       </c>
       <c r="P96">
-        <v>-23.224605216</v>
+        <v>-23.49815208</v>
       </c>
       <c r="Q96">
-        <v>-13.984605216</v>
+        <v>-14.25815208</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.063676394226847</v>
+        <v>1.267251673072217</v>
       </c>
       <c r="T96">
-        <v>13.2663416453003</v>
+        <v>15.91960997436037</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03097279389135264</v>
+        <v>0.03064676448196998</v>
       </c>
       <c r="W96">
-        <v>0.2284966152004191</v>
+        <v>0.2285734929351515</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.09678998091047708</v>
+        <v>0.0957711390061563</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2805074019420046</v>
+        <v>0.2824074019420047</v>
       </c>
       <c r="C97">
-        <v>-114.775716370447</v>
+        <v>-116.8204637563627</v>
       </c>
       <c r="D97">
-        <v>42.18428362955299</v>
+        <v>41.84553624363731</v>
       </c>
       <c r="E97">
-        <v>124.17</v>
+        <v>125.876</v>
       </c>
       <c r="F97">
-        <v>162.07</v>
+        <v>163.776</v>
       </c>
       <c r="G97">
         <v>5.11</v>
@@ -9241,37 +9241,37 @@
         <v>3.66</v>
       </c>
       <c r="M97">
-        <v>38.216106</v>
+        <v>38.6183808</v>
       </c>
       <c r="N97">
-        <v>-34.556106</v>
+        <v>-34.9583808</v>
       </c>
       <c r="O97">
-        <v>-11.05795392</v>
+        <v>-11.186681856</v>
       </c>
       <c r="P97">
-        <v>-23.49815208</v>
+        <v>-23.771698944</v>
       </c>
       <c r="Q97">
-        <v>-14.25815208</v>
+        <v>-14.531698944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.267251673072217</v>
+        <v>1.572614591340272</v>
       </c>
       <c r="T97">
-        <v>15.91960997436037</v>
+        <v>19.89951246795047</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03064676448196998</v>
+        <v>0.03032752735194946</v>
       </c>
       <c r="W97">
-        <v>0.2285734929351515</v>
+        <v>0.2286487690504103</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0957711390061563</v>
+        <v>0.09477352297484221</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2824074019420047</v>
+        <v>0.2843074019420047</v>
       </c>
       <c r="C98">
-        <v>-116.8204637563627</v>
+        <v>-118.8598140767953</v>
       </c>
       <c r="D98">
-        <v>41.84553624363731</v>
+        <v>41.51218592320473</v>
       </c>
       <c r="E98">
-        <v>125.876</v>
+        <v>127.582</v>
       </c>
       <c r="F98">
-        <v>163.776</v>
+        <v>165.482</v>
       </c>
       <c r="G98">
         <v>5.11</v>
@@ -9323,37 +9323,37 @@
         <v>3.66</v>
       </c>
       <c r="M98">
-        <v>38.6183808</v>
+        <v>39.0206556</v>
       </c>
       <c r="N98">
-        <v>-34.9583808</v>
+        <v>-35.3606556</v>
       </c>
       <c r="O98">
-        <v>-11.186681856</v>
+        <v>-11.315409792</v>
       </c>
       <c r="P98">
-        <v>-23.771698944</v>
+        <v>-24.045245808</v>
       </c>
       <c r="Q98">
-        <v>-14.531698944</v>
+        <v>-14.805245808</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.572614591340267</v>
+        <v>2.081552788453689</v>
       </c>
       <c r="T98">
-        <v>19.89951246795042</v>
+        <v>26.53268329060056</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03032752735194947</v>
+        <v>0.03001487243079535</v>
       </c>
       <c r="W98">
-        <v>0.2286487690504103</v>
+        <v>0.2287224930808185</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.09477352297484198</v>
+        <v>0.09379647634623556</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2843074019420047</v>
+        <v>0.2862074019420047</v>
       </c>
       <c r="C99">
-        <v>-118.8598140767953</v>
+        <v>-120.8938952948316</v>
       </c>
       <c r="D99">
-        <v>41.51218592320473</v>
+        <v>41.18410470516838</v>
       </c>
       <c r="E99">
-        <v>127.582</v>
+        <v>129.288</v>
       </c>
       <c r="F99">
-        <v>165.482</v>
+        <v>167.188</v>
       </c>
       <c r="G99">
         <v>5.11</v>
@@ -9405,37 +9405,37 @@
         <v>3.66</v>
       </c>
       <c r="M99">
-        <v>39.0206556</v>
+        <v>39.4229304</v>
       </c>
       <c r="N99">
-        <v>-35.3606556</v>
+        <v>-35.7629304</v>
       </c>
       <c r="O99">
-        <v>-11.315409792</v>
+        <v>-11.444137728</v>
       </c>
       <c r="P99">
-        <v>-24.045245808</v>
+        <v>-24.318792672</v>
       </c>
       <c r="Q99">
-        <v>-14.805245808</v>
+        <v>-15.078792672</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.081552788453689</v>
+        <v>3.099429182680534</v>
       </c>
       <c r="T99">
-        <v>26.53268329060056</v>
+        <v>39.79902493590083</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03001487243079535</v>
+        <v>0.02970859822231784</v>
       </c>
       <c r="W99">
-        <v>0.2287224930808185</v>
+        <v>0.2287947125391775</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.09379647634623556</v>
+        <v>0.09283936944474314</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2862074019420047</v>
+        <v>0.2881074019420046</v>
       </c>
       <c r="C100">
-        <v>-120.8938952948316</v>
+        <v>-122.9228313599814</v>
       </c>
       <c r="D100">
-        <v>41.18410470516838</v>
+        <v>40.86116864001859</v>
       </c>
       <c r="E100">
-        <v>129.288</v>
+        <v>130.994</v>
       </c>
       <c r="F100">
-        <v>167.188</v>
+        <v>168.894</v>
       </c>
       <c r="G100">
         <v>5.11</v>
@@ -9487,37 +9487,37 @@
         <v>3.66</v>
       </c>
       <c r="M100">
-        <v>39.4229304</v>
+        <v>39.82520520000001</v>
       </c>
       <c r="N100">
-        <v>-35.7629304</v>
+        <v>-36.1652052</v>
       </c>
       <c r="O100">
-        <v>-11.444137728</v>
+        <v>-11.572865664</v>
       </c>
       <c r="P100">
-        <v>-24.318792672</v>
+        <v>-24.592339536</v>
       </c>
       <c r="Q100">
-        <v>-15.078792672</v>
+        <v>-15.352339536</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.099429182680534</v>
+        <v>6.153058365361068</v>
       </c>
       <c r="T100">
-        <v>39.79902493590083</v>
+        <v>79.59804987180166</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02970859822231784</v>
+        <v>0.02940851137158735</v>
       </c>
       <c r="W100">
-        <v>0.2287947125391775</v>
+        <v>0.2288654730185797</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.09283936944474314</v>
+        <v>0.09190159803621056</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2881074019420046</v>
-      </c>
-      <c r="C101">
-        <v>-122.9228313599814</v>
-      </c>
-      <c r="D101">
-        <v>40.86116864001859</v>
-      </c>
-      <c r="E101">
-        <v>130.994</v>
-      </c>
-      <c r="F101">
-        <v>168.894</v>
-      </c>
-      <c r="G101">
-        <v>5.11</v>
-      </c>
-      <c r="H101">
-        <v>132.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.9</v>
-      </c>
-      <c r="K101">
-        <v>9.24</v>
-      </c>
-      <c r="L101">
-        <v>3.66</v>
-      </c>
-      <c r="M101">
-        <v>39.82520520000001</v>
-      </c>
-      <c r="N101">
-        <v>-36.1652052</v>
-      </c>
-      <c r="O101">
-        <v>-11.572865664</v>
-      </c>
-      <c r="P101">
-        <v>-24.592339536</v>
-      </c>
-      <c r="Q101">
-        <v>-15.352339536</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.153058365361068</v>
-      </c>
-      <c r="T101">
-        <v>79.59804987180166</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02940851137158735</v>
-      </c>
-      <c r="W101">
-        <v>0.2288654730185797</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.09190159803621056</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
